--- a/public/Daily Sadhana.xlsx
+++ b/public/Daily Sadhana.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sahaa\Documents\github_anandasvarupa\give_web\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8816264A-140B-4C26-9259-258AA92B200F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38CE409-430D-413E-981A-618BE0ABA058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BS-4" sheetId="1" r:id="rId1"/>
     <sheet name="BS-5" sheetId="2" r:id="rId2"/>
     <sheet name="BS-Ekacakra" sheetId="3" r:id="rId3"/>
+    <sheet name="BS-2-English" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="544">
   <si>
     <t>url</t>
   </si>
@@ -1612,6 +1613,54 @@
   <si>
     <t>Today's listening to Srila Prabhupada - 289</t>
   </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1120</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1121</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1122</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1123</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1124</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1125</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1126</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1127</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1128</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1129</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1130</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1131</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1132</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1133</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1134</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1135</t>
+  </si>
 </sst>
 </file>
 
@@ -1621,7 +1670,7 @@
     <numFmt numFmtId="164" formatCode="mmm\ d\,\ yy"/>
     <numFmt numFmtId="165" formatCode="mmm\ d\,\ yyyy"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1658,6 +1707,11 @@
       <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -60549,4 +60603,249 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2DB8064-9FCF-4672-A5DD-AAA1AF5AE7B8}">
+  <dimension ref="A1:Z17"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="50.90625" customWidth="1"/>
+    <col min="2" max="2" width="38.90625" customWidth="1"/>
+    <col min="3" max="3" width="28.90625" customWidth="1"/>
+    <col min="4" max="4" width="21.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+    </row>
+    <row r="2" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="C3" s="7">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>448</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="C4" s="7">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="C5" s="7">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>450</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="C6" s="7">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="C7" s="7">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="C8" s="7">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="C9" s="7">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="C11" s="7">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="C12" s="7">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="C13" s="7">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="C14" s="7">
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="C15" s="7">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="C16" s="7">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="C17" s="7">
+        <v>46295</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://www.youtube.com/watch?v=1Ilgi75Y6Ac&amp;t=9s" xr:uid="{BEFFE2FC-FF84-4042-B8EC-77144312CABC}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{90F813C6-4FEA-4DED-83BD-5034A555CC22}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{B1C314CD-370C-4CA6-9FE8-1ED3943E31D4}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{A17D0F69-B2D0-46D9-B6F6-66C068704A56}"/>
+    <hyperlink ref="A6" r:id="rId5" display="https://www.youtube.com/watch?v=zgLWXkOMOGE&amp;t=20s" xr:uid="{9779AA05-4C44-47F0-B170-2FE8FB47B3BE}"/>
+    <hyperlink ref="A7" r:id="rId6" display="https://www.youtube.com/watch?v=r-DPvpwMOdw&amp;t=144s" xr:uid="{0276A8C9-E8B0-4D6A-9CEF-9F2AAB75C880}"/>
+    <hyperlink ref="A8" r:id="rId7" xr:uid="{F19BACE9-B34B-4C91-86EB-670079642404}"/>
+    <hyperlink ref="A9" r:id="rId8" xr:uid="{7CBC5B68-7623-491F-8129-5C469970DB0C}"/>
+    <hyperlink ref="A10" r:id="rId9" xr:uid="{6503D671-ACE1-4397-8206-9F396EA2AA88}"/>
+    <hyperlink ref="A11" r:id="rId10" xr:uid="{3DAB877A-772C-41D4-9E5C-E44AFD14063A}"/>
+    <hyperlink ref="A12" r:id="rId11" display="https://www.youtube.com/watch?v=X6XNEMBmPrk&amp;t=149s" xr:uid="{3D449635-2546-48EE-9157-EDAADD1D323B}"/>
+    <hyperlink ref="A13" r:id="rId12" xr:uid="{ADF479E2-4D26-4E3A-8975-974F3667CD5A}"/>
+    <hyperlink ref="A14" r:id="rId13" xr:uid="{DE18D8BB-EB17-4E0B-B273-35819EBED68A}"/>
+    <hyperlink ref="A15" r:id="rId14" display="https://www.youtube.com/watch?v=qCOWcKURVzk&amp;t=1s" xr:uid="{6A11C7B1-0010-43D5-9F17-1F6D51AD59E6}"/>
+    <hyperlink ref="A16" r:id="rId15" xr:uid="{AD44B6A8-1E3C-44E6-A013-F6004413BDEA}"/>
+    <hyperlink ref="A17" r:id="rId16" display="https://www.youtube.com/watch?v=-NHHdVWUcwo&amp;t=3s" xr:uid="{B9FC0606-31ED-4E7D-91D6-1FC640AB21A4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/public/Daily Sadhana.xlsx
+++ b/public/Daily Sadhana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sahaa\Documents\github_anandasvarupa\give_web\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38CE409-430D-413E-981A-618BE0ABA058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD15EB56-47F7-4302-A672-84AE5291562B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5170" yWindow="3470" windowWidth="14030" windowHeight="6610" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BS-4" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="611">
   <si>
     <t>url</t>
   </si>
@@ -1661,6 +1661,207 @@
   <si>
     <t>Today's listening to Srila Prabhupada - 1135</t>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=CftLOpEg8JM</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zsCVrqVMcx8</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ECzOXYCimqs</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=YLO02uvW1jw</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zsTa0XXJ7qo</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=CWoOXeF3Yxg</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=bE_ippUqgo0</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=AwMpoLPpteI</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=US55Ai355ag</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yPoaMCjJln4</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=4x6esIcwhK0</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=j7T1MKt-ydA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=CL3MjqFWpRk</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=EtaDH-J1ZEY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=STe9eE9d6cM</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=bXGdE7t5DHg</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=1LDGcLBVSuk</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=GvZbTG9Hwj8</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zhOO4Svlg0g</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Tw3vp5zupx0</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KX4XKIQ558I</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=5IdV68D4A90</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=aN2y6k1zMa4</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PSEXwM2qQmM</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=8siMw00cRt8</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=6S_PSfha1ag</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=bYF_FX-vZ78</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=f8AoUoiTXes</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=iUJA3Bh8NzE</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=GiMnzOTvMOM</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ixeML2iYD3w</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=H9h2FMQPUeg</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yi3n-KpYdVY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=GDeMHEPvhIw</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=tp3q1RMK2cw</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VTg-IZm0q34</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=OaIUX41Sz48</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VcS7IKB-d8s</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3iX21gh2t0Q</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yiug7xQlTAI</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1136</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1137</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1138</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1139</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1140</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1141</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1142</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1143</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1144</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1145</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1146</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1147</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1148</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1149</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1150</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1151</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1152</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1153</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1154</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1155</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1156</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1157</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1158</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1159</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1160</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1161</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1162</t>
+  </si>
 </sst>
 </file>
 
@@ -1802,7 +2003,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1843,6 +2044,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -60607,7 +60809,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2DB8064-9FCF-4672-A5DD-AAA1AF5AE7B8}">
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z44"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.90625" customWidth="1"/>
@@ -60663,7 +60865,7 @@
     </row>
     <row r="3" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>447</v>
+        <v>544</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>529</v>
@@ -60674,7 +60876,7 @@
     </row>
     <row r="4" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>448</v>
+        <v>545</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>530</v>
@@ -60685,7 +60887,7 @@
     </row>
     <row r="5" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>449</v>
+        <v>546</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>531</v>
@@ -60696,7 +60898,7 @@
     </row>
     <row r="6" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>450</v>
+        <v>547</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>532</v>
@@ -60707,7 +60909,7 @@
     </row>
     <row r="7" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>451</v>
+        <v>548</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>533</v>
@@ -60718,7 +60920,7 @@
     </row>
     <row r="8" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>452</v>
+        <v>549</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>534</v>
@@ -60729,7 +60931,7 @@
     </row>
     <row r="9" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>453</v>
+        <v>550</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>535</v>
@@ -60740,7 +60942,7 @@
     </row>
     <row r="10" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>454</v>
+        <v>551</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>536</v>
@@ -60751,7 +60953,7 @@
     </row>
     <row r="11" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>455</v>
+        <v>552</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>537</v>
@@ -60762,7 +60964,7 @@
     </row>
     <row r="12" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>456</v>
+        <v>553</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>538</v>
@@ -60773,7 +60975,7 @@
     </row>
     <row r="13" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>457</v>
+        <v>554</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>539</v>
@@ -60784,7 +60986,7 @@
     </row>
     <row r="14" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>458</v>
+        <v>555</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>540</v>
@@ -60795,7 +60997,7 @@
     </row>
     <row r="15" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>459</v>
+        <v>556</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>541</v>
@@ -60806,7 +61008,7 @@
     </row>
     <row r="16" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>460</v>
+        <v>557</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>542</v>
@@ -60817,34 +61019,317 @@
     </row>
     <row r="17" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>312</v>
+        <v>558</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>543</v>
       </c>
       <c r="C17" s="7">
         <v>46295</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="C18" s="7">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>560</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="C19" s="7">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>561</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="C20" s="7">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>562</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="C21" s="7">
+        <v>46299</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>563</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="C22" s="7">
+        <v>46300</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>564</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="C23" s="7">
+        <v>46301</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>565</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="C24" s="7">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>566</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="C25" s="7">
+        <v>46303</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>567</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="C26" s="7">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>568</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="C27" s="7">
+        <v>46305</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>569</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="C28" s="7">
+        <v>46306</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>570</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="C29" s="7">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>571</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="C30" s="7">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>572</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="C31" s="7">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>573</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="C32" s="7">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>574</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="C33" s="7">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>422</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="C34" s="7">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>575</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="C35" s="7">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>576</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="C36" s="7">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>577</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="C37" s="7">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>578</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="C38" s="7">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>579</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="C39" s="7">
+        <v>46317</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>580</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="C40" s="7">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>581</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="C41" s="7">
+        <v>46319</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>582</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="C42" s="7">
+        <v>46320</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>366</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="C43" s="7">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>583</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="C44" s="7">
+        <v>46322</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.youtube.com/watch?v=1Ilgi75Y6Ac&amp;t=9s" xr:uid="{BEFFE2FC-FF84-4042-B8EC-77144312CABC}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{90F813C6-4FEA-4DED-83BD-5034A555CC22}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{B1C314CD-370C-4CA6-9FE8-1ED3943E31D4}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{A17D0F69-B2D0-46D9-B6F6-66C068704A56}"/>
-    <hyperlink ref="A6" r:id="rId5" display="https://www.youtube.com/watch?v=zgLWXkOMOGE&amp;t=20s" xr:uid="{9779AA05-4C44-47F0-B170-2FE8FB47B3BE}"/>
-    <hyperlink ref="A7" r:id="rId6" display="https://www.youtube.com/watch?v=r-DPvpwMOdw&amp;t=144s" xr:uid="{0276A8C9-E8B0-4D6A-9CEF-9F2AAB75C880}"/>
-    <hyperlink ref="A8" r:id="rId7" xr:uid="{F19BACE9-B34B-4C91-86EB-670079642404}"/>
-    <hyperlink ref="A9" r:id="rId8" xr:uid="{7CBC5B68-7623-491F-8129-5C469970DB0C}"/>
-    <hyperlink ref="A10" r:id="rId9" xr:uid="{6503D671-ACE1-4397-8206-9F396EA2AA88}"/>
-    <hyperlink ref="A11" r:id="rId10" xr:uid="{3DAB877A-772C-41D4-9E5C-E44AFD14063A}"/>
-    <hyperlink ref="A12" r:id="rId11" display="https://www.youtube.com/watch?v=X6XNEMBmPrk&amp;t=149s" xr:uid="{3D449635-2546-48EE-9157-EDAADD1D323B}"/>
-    <hyperlink ref="A13" r:id="rId12" xr:uid="{ADF479E2-4D26-4E3A-8975-974F3667CD5A}"/>
-    <hyperlink ref="A14" r:id="rId13" xr:uid="{DE18D8BB-EB17-4E0B-B273-35819EBED68A}"/>
-    <hyperlink ref="A15" r:id="rId14" display="https://www.youtube.com/watch?v=qCOWcKURVzk&amp;t=1s" xr:uid="{6A11C7B1-0010-43D5-9F17-1F6D51AD59E6}"/>
-    <hyperlink ref="A16" r:id="rId15" xr:uid="{AD44B6A8-1E3C-44E6-A013-F6004413BDEA}"/>
-    <hyperlink ref="A17" r:id="rId16" display="https://www.youtube.com/watch?v=-NHHdVWUcwo&amp;t=3s" xr:uid="{B9FC0606-31ED-4E7D-91D6-1FC640AB21A4}"/>
+    <hyperlink ref="A18" r:id="rId2" xr:uid="{266B1484-6826-4EF7-BFC0-E28E4199D83A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/Daily Sadhana.xlsx
+++ b/public/Daily Sadhana.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sahaa\Documents\github_anandasvarupa\give_web\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD15EB56-47F7-4302-A672-84AE5291562B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{567053E3-F29A-4970-A043-06ADD0DB464C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5170" yWindow="3470" windowWidth="14030" windowHeight="6610" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BS-4" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="729">
   <si>
     <t>url</t>
   </si>
@@ -1861,6 +1861,360 @@
   </si>
   <si>
     <t>Today's listening to Srila Prabhupada - 1162</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Zp9COAhA5Qg</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=iT7CUPzFbRQ</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=vuSYcVsLKhY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=MJsviZtSPFc</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Ya86jfgQxPU</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=jJSRiLY_hKo</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=1fPXxQTCPKQ</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=UYxQk_XPbK0</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=RlpBLX3JuYs</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=lYmJpn9Y9Rc</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zLukfF9n0q4</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=G3QwYAUfSQY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3OuM3M9TXkg</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yT7mrbT76IA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=XDoquCuFKGk</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=qYqJ9IOnwBY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-LbZypTQTSA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Ne58ALWRs68</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hE9f3FTjhog</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=xWL1pFNcmgU</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Q24FZ2FRwGQ</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PSdAotICn2I</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=GTeBLRi-Hho</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=AW19y7ztyKs</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=nbGi3a_tyi0</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=QqTdOn-fxO4</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=z2dGDx3u5p0</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=rPfM-T7cae8</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0dXu0tUYZkU</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=HLgoQEBcm6o</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ruWNJ2f_KJs</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=JzzYCOUZitA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=obCYVOA0duE</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Lxwh9fSrLfo</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=jPbVjbi0gEM</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Yjc7P_-Yuhg</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Mv14PuzubPs</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=vVvHXSohHwA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=X5W0Q8e1sEI</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=TLaRnmjmabE</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=8LGfGpiD-Mk</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=NrBla1RTvTE</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3AZsGCz5Y0U</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=M1sIXwvAUTY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=xtjAViL6NzY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=SIeo5ExlIzs</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Ai0jdNcEMHw</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=NTkoR9-OxkY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=TG60mjnVoaw</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=SJJYT2SIvYU</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zszsN5Dcgxc</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gKC8gUdN9vw</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=6j0AsvSGtp0</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=WPrboj55c-k</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=U11n0ipItzk</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ZIwqXVpiiRg</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=e5WktKrdG1E</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 290</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 291</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 292</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 293</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 294</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 295</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 296</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 297</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 298</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 299</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 300</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 301</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 302</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 303</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 304</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 305</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 306</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 307</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 308</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 309</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 310</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 311</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 312</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 313</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 314</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 315</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 316</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 317</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 318</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 319</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 320</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 321</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 322</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 323</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 324</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 325</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 326</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 327</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 328</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 329</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 330</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 331</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 332</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 333</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 334</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 335</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 336</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 337</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 338</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 339</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 340</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 341</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 342</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 343</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 344</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 345</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 346</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 347</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 348</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 349</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 350</t>
   </si>
 </sst>
 </file>
@@ -2268,7 +2622,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z196"/>
+  <dimension ref="A1:Z257"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.81640625" customWidth="1"/>
@@ -4453,6 +4807,677 @@
       </c>
       <c r="C196" s="5">
         <v>46300</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="B197" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="C197" s="5">
+        <v>46301</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="11" t="s">
+        <v>612</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="C198" s="5">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>670</v>
+      </c>
+      <c r="C199" s="5">
+        <v>46303</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="11" t="s">
+        <v>614</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="C200" s="5">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="C201" s="5">
+        <v>46305</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>673</v>
+      </c>
+      <c r="C202" s="5">
+        <v>46306</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>674</v>
+      </c>
+      <c r="C203" s="5">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="11" t="s">
+        <v>617</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="C204" s="5">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="11" t="s">
+        <v>618</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="C205" s="5">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>677</v>
+      </c>
+      <c r="C206" s="5">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="C207" s="5">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="11" t="s">
+        <v>621</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>679</v>
+      </c>
+      <c r="C208" s="5">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="11" t="s">
+        <v>622</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="C209" s="5">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="11" t="s">
+        <v>623</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="C210" s="5">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="11" t="s">
+        <v>624</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="C211" s="5">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="11" t="s">
+        <v>625</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="C212" s="5">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="C213" s="5">
+        <v>46317</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="11" t="s">
+        <v>627</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="C214" s="5">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="11" t="s">
+        <v>628</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>686</v>
+      </c>
+      <c r="C215" s="5">
+        <v>46319</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="C216" s="5">
+        <v>46320</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>688</v>
+      </c>
+      <c r="C217" s="5">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>689</v>
+      </c>
+      <c r="C218" s="5">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>690</v>
+      </c>
+      <c r="C219" s="5">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A220" s="11" t="s">
+        <v>632</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>691</v>
+      </c>
+      <c r="C220" s="5">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A221" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="C221" s="5">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A222" s="11" t="s">
+        <v>634</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="C222" s="5">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A223" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="C223" s="5">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A224" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="C224" s="5">
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="C225" s="5">
+        <v>46329</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>697</v>
+      </c>
+      <c r="C226" s="5">
+        <v>46330</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>698</v>
+      </c>
+      <c r="C227" s="5">
+        <v>46331</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="C228" s="5">
+        <v>46332</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="C229" s="5">
+        <v>46333</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="11" t="s">
+        <v>642</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="C230" s="5">
+        <v>46334</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>702</v>
+      </c>
+      <c r="C231" s="5">
+        <v>46335</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="11" t="s">
+        <v>643</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>703</v>
+      </c>
+      <c r="C232" s="5">
+        <v>46336</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="11" t="s">
+        <v>644</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>704</v>
+      </c>
+      <c r="C233" s="5">
+        <v>46337</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="C234" s="5">
+        <v>46338</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="11" t="s">
+        <v>646</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>706</v>
+      </c>
+      <c r="C235" s="5">
+        <v>46339</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="11" t="s">
+        <v>647</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="C236" s="5">
+        <v>46340</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A237" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="C237" s="5">
+        <v>46341</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A238" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="C238" s="5">
+        <v>46342</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A239" s="11" t="s">
+        <v>649</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>710</v>
+      </c>
+      <c r="C239" s="5">
+        <v>46343</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="11" t="s">
+        <v>650</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="C240" s="5">
+        <v>46344</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="C241" s="5">
+        <v>46345</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A242" s="11" t="s">
+        <v>652</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="C242" s="5">
+        <v>46346</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A243" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="C243" s="5">
+        <v>46347</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="11" t="s">
+        <v>654</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="C244" s="5">
+        <v>46348</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="11" t="s">
+        <v>655</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="C245" s="5">
+        <v>46349</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A246" s="11" t="s">
+        <v>656</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="C246" s="5">
+        <v>46350</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A247" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="C247" s="5">
+        <v>46351</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A248" s="11" t="s">
+        <v>658</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="C248" s="5">
+        <v>46352</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A249" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>720</v>
+      </c>
+      <c r="C249" s="5">
+        <v>46353</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>721</v>
+      </c>
+      <c r="C250" s="5">
+        <v>46354</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A251" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="C251" s="5">
+        <v>46355</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A252" s="11" t="s">
+        <v>662</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="C252" s="5">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="11" t="s">
+        <v>663</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="C253" s="5">
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A254" s="11" t="s">
+        <v>664</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>725</v>
+      </c>
+      <c r="C254" s="5">
+        <v>46358</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A255" s="11" t="s">
+        <v>665</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>726</v>
+      </c>
+      <c r="C255" s="5">
+        <v>46359</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A256" s="11" t="s">
+        <v>666</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="C256" s="5">
+        <v>46360</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="11" t="s">
+        <v>667</v>
+      </c>
+      <c r="B257" s="6" t="s">
+        <v>728</v>
+      </c>
+      <c r="C257" s="5">
+        <v>46361</v>
       </c>
     </row>
   </sheetData>
@@ -4653,9 +5678,70 @@
     <hyperlink ref="A194" r:id="rId193" display="https://www.youtube.com/watch?v=7rdJOSgHgg4&amp;t=559s" xr:uid="{E32B95CD-2286-4E4C-A479-248D65243279}"/>
     <hyperlink ref="A195" r:id="rId194" xr:uid="{1D736B2E-23D1-45FB-932F-B87290328240}"/>
     <hyperlink ref="A196" r:id="rId195" display="https://www.youtube.com/watch?v=tS58CDMrFxA&amp;t=23s" xr:uid="{DB8FD2AE-9C9C-411A-AD03-265E506F09A4}"/>
+    <hyperlink ref="A197" r:id="rId196" xr:uid="{E4B65CB2-B12B-4E01-8AC0-A597539B987B}"/>
+    <hyperlink ref="A198" r:id="rId197" display="https://www.youtube.com/watch?v=iT7CUPzFbRQ&amp;t=9s" xr:uid="{03D5DD18-B3A2-4166-9306-8D8E310FB194}"/>
+    <hyperlink ref="A199" r:id="rId198" display="https://www.youtube.com/watch?v=vuSYcVsLKhY&amp;t=1531s" xr:uid="{FCF6576E-49EB-4905-835D-E0E61E7D7C09}"/>
+    <hyperlink ref="A200" r:id="rId199" display="https://www.youtube.com/watch?v=MJsviZtSPFc&amp;t=12s" xr:uid="{5D82DE7F-845F-41F6-97C2-41B32B13446C}"/>
+    <hyperlink ref="A201" r:id="rId200" display="https://www.youtube.com/watch?v=Ya86jfgQxPU&amp;t=49s" xr:uid="{BB17B408-E0BC-45D7-9480-EC95BF3FE036}"/>
+    <hyperlink ref="A202" r:id="rId201" display="https://www.youtube.com/watch?v=jJSRiLY_hKo&amp;t=2s" xr:uid="{DAB7C84E-2EF4-4BA0-9B84-7E8E344C6FDA}"/>
+    <hyperlink ref="A203" r:id="rId202" display="https://www.youtube.com/watch?v=-NHHdVWUcwo&amp;t=2s" xr:uid="{39702C48-ED16-41E2-9B83-4CF009392037}"/>
+    <hyperlink ref="A204" r:id="rId203" display="https://www.youtube.com/watch?v=1fPXxQTCPKQ&amp;t=1s" xr:uid="{5F0796F1-C901-49FF-9685-1724B25A92BD}"/>
+    <hyperlink ref="A205" r:id="rId204" xr:uid="{7F7F37EC-AE0D-4B4F-AE54-435ACDABD357}"/>
+    <hyperlink ref="A206" r:id="rId205" xr:uid="{28A02385-99F5-4B48-8FA7-CB61099334FE}"/>
+    <hyperlink ref="A207" r:id="rId206" xr:uid="{EF421BC2-8680-4B44-B50D-9AF9F4F94D7D}"/>
+    <hyperlink ref="A208" r:id="rId207" xr:uid="{B4309A8B-5E76-40B0-8EBE-51A99C1B6B64}"/>
+    <hyperlink ref="A209" r:id="rId208" display="https://www.youtube.com/watch?v=G3QwYAUfSQY&amp;t=3s" xr:uid="{FD8F3F1A-D96D-4813-8F13-205313BEC996}"/>
+    <hyperlink ref="A210" r:id="rId209" display="https://www.youtube.com/watch?v=3OuM3M9TXkg&amp;t=1s" xr:uid="{4C13E472-407C-4D30-AD35-CE1560990040}"/>
+    <hyperlink ref="A211" r:id="rId210" xr:uid="{8057C929-063D-416B-B3A0-44EF3B162EAD}"/>
+    <hyperlink ref="A212" r:id="rId211" display="https://www.youtube.com/watch?v=XDoquCuFKGk&amp;t=242s" xr:uid="{FD395589-ACB1-471F-BCA1-4D7AEA152DA9}"/>
+    <hyperlink ref="A213" r:id="rId212" display="https://www.youtube.com/watch?v=qYqJ9IOnwBY&amp;t=47s" xr:uid="{779AA836-A8E8-42A2-8917-048F7732C76B}"/>
+    <hyperlink ref="A214" r:id="rId213" xr:uid="{7C01700A-FFBF-4148-9C45-D838436607E5}"/>
+    <hyperlink ref="A215" r:id="rId214" display="https://www.youtube.com/watch?v=Ne58ALWRs68&amp;t=46s" xr:uid="{871D03F6-DB4B-44D4-A5AB-FFCA82C6162A}"/>
+    <hyperlink ref="A216" r:id="rId215" display="https://www.youtube.com/watch?v=hE9f3FTjhog&amp;t=28s" xr:uid="{8BF56221-2873-40B7-ACA9-5AE2612AD0ED}"/>
+    <hyperlink ref="A217" r:id="rId216" xr:uid="{DEA7A172-FE18-4C53-B4BF-B192B616E062}"/>
+    <hyperlink ref="A218" r:id="rId217" display="https://www.youtube.com/watch?v=8siMw00cRt8&amp;t=1s" xr:uid="{61363400-5B86-4045-917C-2549E3B76F8C}"/>
+    <hyperlink ref="A219" r:id="rId218" display="https://www.youtube.com/watch?v=Q24FZ2FRwGQ&amp;t=2s" xr:uid="{1A0379AD-A566-40C0-ACA4-3A82921711E3}"/>
+    <hyperlink ref="A220" r:id="rId219" xr:uid="{00C42461-1CE0-4108-93E1-B64DA761D30E}"/>
+    <hyperlink ref="A221" r:id="rId220" display="https://www.youtube.com/watch?v=GTeBLRi-Hho&amp;t=1s" xr:uid="{EC32F977-E1E1-4813-A5C4-01ABE57CDE5B}"/>
+    <hyperlink ref="A222" r:id="rId221" display="https://www.youtube.com/watch?v=AW19y7ztyKs&amp;t=1361s" xr:uid="{D12ECBC5-59D0-40B1-A6DA-503EC728EDD2}"/>
+    <hyperlink ref="A223" r:id="rId222" display="https://www.youtube.com/watch?v=nbGi3a_tyi0&amp;t=2s" xr:uid="{3BF432C5-147E-4A5C-B33E-D80DD0743B67}"/>
+    <hyperlink ref="A224" r:id="rId223" display="https://www.youtube.com/watch?v=QqTdOn-fxO4&amp;t=18s" xr:uid="{6A4ACFBB-1200-4E68-BA95-A85AAD1D3929}"/>
+    <hyperlink ref="A225" r:id="rId224" display="https://www.youtube.com/watch?v=z2dGDx3u5p0&amp;t=232s" xr:uid="{34F2253F-813C-4860-9A84-23F06BC6878E}"/>
+    <hyperlink ref="A226" r:id="rId225" display="https://www.youtube.com/watch?v=rPfM-T7cae8&amp;t=1s" xr:uid="{74AAF0A0-70CD-43B1-A4D7-1FCD5F17ADEC}"/>
+    <hyperlink ref="A227" r:id="rId226" xr:uid="{48F5DDD9-FB9E-448F-9BA1-D55FFE2F4CAA}"/>
+    <hyperlink ref="A228" r:id="rId227" display="https://www.youtube.com/watch?v=HLgoQEBcm6o&amp;t=125s" xr:uid="{009E461F-8EA2-4956-AC19-57A91999B185}"/>
+    <hyperlink ref="A229" r:id="rId228" display="https://www.youtube.com/watch?v=ruWNJ2f_KJs&amp;t=16s" xr:uid="{AF149A80-8EE8-432D-9D5F-0A71A2257C57}"/>
+    <hyperlink ref="A230" r:id="rId229" xr:uid="{4B07CB69-A098-49EA-9286-AD36F5E38199}"/>
+    <hyperlink ref="A231" r:id="rId230" display="https://www.youtube.com/watch?v=ixeML2iYD3w&amp;t=3s" xr:uid="{E374C6E3-87CB-43BC-9062-7AE4D138A5F8}"/>
+    <hyperlink ref="A232" r:id="rId231" xr:uid="{60D05EB6-C738-4FCD-BB56-49FCA0D06734}"/>
+    <hyperlink ref="A233" r:id="rId232" display="https://www.youtube.com/watch?v=Lxwh9fSrLfo&amp;t=4s" xr:uid="{24A7BF26-7C78-438F-A9D6-23D3D691B5E5}"/>
+    <hyperlink ref="A234" r:id="rId233" xr:uid="{3A2865E5-B1B2-4303-9CED-3F1CA45BF87A}"/>
+    <hyperlink ref="A235" r:id="rId234" display="https://www.youtube.com/watch?v=Yjc7P_-Yuhg&amp;t=42s" xr:uid="{8EE77B49-4A60-4CAC-96CB-42922F6FFD0A}"/>
+    <hyperlink ref="A236" r:id="rId235" display="https://www.youtube.com/watch?v=Mv14PuzubPs&amp;t=2s" xr:uid="{88B91973-1C3F-4180-B2E1-3E388CC4E0D7}"/>
+    <hyperlink ref="A237" r:id="rId236" display="https://www.youtube.com/watch?v=vVvHXSohHwA&amp;t=4s" xr:uid="{C779FBAC-53A5-4195-BA8E-4388426C293F}"/>
+    <hyperlink ref="A238" r:id="rId237" display="https://www.youtube.com/watch?v=vVvHXSohHwA&amp;t=4s" xr:uid="{006D5A70-191F-4BD7-9A64-E9388AC50E09}"/>
+    <hyperlink ref="A239" r:id="rId238" xr:uid="{E8400F40-BBA4-4804-9A65-ED3053E03175}"/>
+    <hyperlink ref="A240" r:id="rId239" display="https://www.youtube.com/watch?v=TLaRnmjmabE&amp;t=2s" xr:uid="{3BDC2F40-9180-465E-846A-DD36945495B6}"/>
+    <hyperlink ref="A241" r:id="rId240" display="https://www.youtube.com/watch?v=8LGfGpiD-Mk&amp;t=11s" xr:uid="{BF824314-62F6-4C33-9EA0-67AB9F6ED4D1}"/>
+    <hyperlink ref="A242" r:id="rId241" display="https://www.youtube.com/watch?v=NrBla1RTvTE&amp;t=29s" xr:uid="{443F2BC2-528D-48DC-AD7B-45D92CB082B9}"/>
+    <hyperlink ref="A243" r:id="rId242" xr:uid="{A26F099A-748C-47FF-AC65-F15FE1BEF780}"/>
+    <hyperlink ref="A244" r:id="rId243" xr:uid="{EF832A53-6B4A-414C-A6F8-E7E0C940DAF0}"/>
+    <hyperlink ref="A245" r:id="rId244" xr:uid="{D93EAFED-0419-4F24-89B8-D71B8CAB2D1C}"/>
+    <hyperlink ref="A246" r:id="rId245" xr:uid="{4611A0EA-3578-4BA6-85D7-BD3377526C5C}"/>
+    <hyperlink ref="A247" r:id="rId246" display="https://www.youtube.com/watch?v=Ai0jdNcEMHw&amp;t=5s" xr:uid="{8A9821D2-0DA1-4ADA-9D60-EE6C70C0DD1D}"/>
+    <hyperlink ref="A248" r:id="rId247" xr:uid="{BA7704B7-81A1-4353-B378-B969AC6AEA36}"/>
+    <hyperlink ref="A249" r:id="rId248" xr:uid="{A58DF97E-ED28-4C85-B29F-9F12D4AEC2DA}"/>
+    <hyperlink ref="A250" r:id="rId249" xr:uid="{4F90980B-32AA-463B-A1A8-039AD9C8DF3C}"/>
+    <hyperlink ref="A251" r:id="rId250" xr:uid="{511630EC-C951-4CF3-8BB4-120E0DED00F5}"/>
+    <hyperlink ref="A252" r:id="rId251" xr:uid="{F36DFBB4-EED3-47E0-85C6-C81AB5744D9E}"/>
+    <hyperlink ref="A253" r:id="rId252" xr:uid="{AF212613-7603-4ABE-B5AE-3059485C321E}"/>
+    <hyperlink ref="A254" r:id="rId253" xr:uid="{4730505C-5190-4288-A31B-25D7606382AE}"/>
+    <hyperlink ref="A255" r:id="rId254" xr:uid="{CE715489-DB4B-4F24-AE09-D3D005CBBB59}"/>
+    <hyperlink ref="A256" r:id="rId255" xr:uid="{9DF8DA76-AB37-4893-9BB0-5D9855894D97}"/>
+    <hyperlink ref="A257" r:id="rId256" xr:uid="{F39C653E-45F8-4B5E-84A8-44FB1DB880F9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId196"/>
+  <pageSetup orientation="portrait" r:id="rId257"/>
 </worksheet>
 </file>
 
@@ -12765,10 +13851,16 @@
       <c r="Y238" s="6"/>
       <c r="Z238" s="6"/>
     </row>
-    <row r="239" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A239" s="6"/>
-      <c r="B239" s="6"/>
-      <c r="C239" s="6"/>
+    <row r="239" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A239" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="C239" s="5">
+        <v>46301</v>
+      </c>
       <c r="D239" s="6"/>
       <c r="E239" s="6"/>
       <c r="F239" s="6"/>
@@ -12793,10 +13885,16 @@
       <c r="Y239" s="6"/>
       <c r="Z239" s="6"/>
     </row>
-    <row r="240" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A240" s="6"/>
-      <c r="B240" s="6"/>
-      <c r="C240" s="6"/>
+    <row r="240" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="11" t="s">
+        <v>612</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="C240" s="5">
+        <v>46302</v>
+      </c>
       <c r="D240" s="6"/>
       <c r="E240" s="6"/>
       <c r="F240" s="6"/>
@@ -12821,10 +13919,16 @@
       <c r="Y240" s="6"/>
       <c r="Z240" s="6"/>
     </row>
-    <row r="241" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A241" s="6"/>
-      <c r="B241" s="6"/>
-      <c r="C241" s="6"/>
+    <row r="241" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="C241" s="5">
+        <v>46303</v>
+      </c>
       <c r="D241" s="6"/>
       <c r="E241" s="6"/>
       <c r="F241" s="6"/>
@@ -12849,10 +13953,16 @@
       <c r="Y241" s="6"/>
       <c r="Z241" s="6"/>
     </row>
-    <row r="242" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A242" s="6"/>
-      <c r="B242" s="6"/>
-      <c r="C242" s="6"/>
+    <row r="242" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A242" s="11" t="s">
+        <v>614</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="C242" s="5">
+        <v>46304</v>
+      </c>
       <c r="D242" s="6"/>
       <c r="E242" s="6"/>
       <c r="F242" s="6"/>
@@ -12877,10 +13987,16 @@
       <c r="Y242" s="6"/>
       <c r="Z242" s="6"/>
     </row>
-    <row r="243" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A243" s="6"/>
-      <c r="B243" s="6"/>
-      <c r="C243" s="6"/>
+    <row r="243" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A243" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="C243" s="5">
+        <v>46305</v>
+      </c>
       <c r="D243" s="6"/>
       <c r="E243" s="6"/>
       <c r="F243" s="6"/>
@@ -12905,10 +14021,16 @@
       <c r="Y243" s="6"/>
       <c r="Z243" s="6"/>
     </row>
-    <row r="244" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A244" s="6"/>
-      <c r="B244" s="6"/>
-      <c r="C244" s="6"/>
+    <row r="244" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="C244" s="5">
+        <v>46306</v>
+      </c>
       <c r="D244" s="6"/>
       <c r="E244" s="6"/>
       <c r="F244" s="6"/>
@@ -12933,10 +14055,16 @@
       <c r="Y244" s="6"/>
       <c r="Z244" s="6"/>
     </row>
-    <row r="245" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A245" s="6"/>
-      <c r="B245" s="6"/>
-      <c r="C245" s="6"/>
+    <row r="245" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="C245" s="5">
+        <v>46307</v>
+      </c>
       <c r="D245" s="6"/>
       <c r="E245" s="6"/>
       <c r="F245" s="6"/>
@@ -12961,10 +14089,16 @@
       <c r="Y245" s="6"/>
       <c r="Z245" s="6"/>
     </row>
-    <row r="246" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A246" s="6"/>
-      <c r="B246" s="6"/>
-      <c r="C246" s="6"/>
+    <row r="246" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A246" s="11" t="s">
+        <v>617</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="C246" s="5">
+        <v>46308</v>
+      </c>
       <c r="D246" s="6"/>
       <c r="E246" s="6"/>
       <c r="F246" s="6"/>
@@ -12989,10 +14123,16 @@
       <c r="Y246" s="6"/>
       <c r="Z246" s="6"/>
     </row>
-    <row r="247" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A247" s="6"/>
-      <c r="B247" s="6"/>
-      <c r="C247" s="6"/>
+    <row r="247" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A247" s="11" t="s">
+        <v>618</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="C247" s="5">
+        <v>46309</v>
+      </c>
       <c r="D247" s="6"/>
       <c r="E247" s="6"/>
       <c r="F247" s="6"/>
@@ -13017,10 +14157,16 @@
       <c r="Y247" s="6"/>
       <c r="Z247" s="6"/>
     </row>
-    <row r="248" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A248" s="6"/>
-      <c r="B248" s="6"/>
-      <c r="C248" s="6"/>
+    <row r="248" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A248" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="C248" s="5">
+        <v>46310</v>
+      </c>
       <c r="D248" s="6"/>
       <c r="E248" s="6"/>
       <c r="F248" s="6"/>
@@ -13045,10 +14191,16 @@
       <c r="Y248" s="6"/>
       <c r="Z248" s="6"/>
     </row>
-    <row r="249" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A249" s="6"/>
-      <c r="B249" s="6"/>
-      <c r="C249" s="6"/>
+    <row r="249" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A249" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="C249" s="5">
+        <v>46311</v>
+      </c>
       <c r="D249" s="6"/>
       <c r="E249" s="6"/>
       <c r="F249" s="6"/>
@@ -13073,10 +14225,16 @@
       <c r="Y249" s="6"/>
       <c r="Z249" s="6"/>
     </row>
-    <row r="250" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A250" s="6"/>
-      <c r="B250" s="6"/>
-      <c r="C250" s="6"/>
+    <row r="250" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="11" t="s">
+        <v>621</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="C250" s="5">
+        <v>46312</v>
+      </c>
       <c r="D250" s="6"/>
       <c r="E250" s="6"/>
       <c r="F250" s="6"/>
@@ -13101,10 +14259,16 @@
       <c r="Y250" s="6"/>
       <c r="Z250" s="6"/>
     </row>
-    <row r="251" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A251" s="6"/>
-      <c r="B251" s="6"/>
-      <c r="C251" s="6"/>
+    <row r="251" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A251" s="11" t="s">
+        <v>622</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="C251" s="5">
+        <v>46313</v>
+      </c>
       <c r="D251" s="6"/>
       <c r="E251" s="6"/>
       <c r="F251" s="6"/>
@@ -13129,10 +14293,16 @@
       <c r="Y251" s="6"/>
       <c r="Z251" s="6"/>
     </row>
-    <row r="252" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A252" s="6"/>
-      <c r="B252" s="6"/>
-      <c r="C252" s="6"/>
+    <row r="252" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A252" s="11" t="s">
+        <v>623</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="C252" s="5">
+        <v>46314</v>
+      </c>
       <c r="D252" s="6"/>
       <c r="E252" s="6"/>
       <c r="F252" s="6"/>
@@ -13157,10 +14327,16 @@
       <c r="Y252" s="6"/>
       <c r="Z252" s="6"/>
     </row>
-    <row r="253" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A253" s="6"/>
-      <c r="B253" s="6"/>
-      <c r="C253" s="6"/>
+    <row r="253" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="11" t="s">
+        <v>624</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="C253" s="5">
+        <v>46315</v>
+      </c>
       <c r="D253" s="6"/>
       <c r="E253" s="6"/>
       <c r="F253" s="6"/>
@@ -13185,10 +14361,16 @@
       <c r="Y253" s="6"/>
       <c r="Z253" s="6"/>
     </row>
-    <row r="254" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="6"/>
-      <c r="B254" s="6"/>
-      <c r="C254" s="6"/>
+    <row r="254" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A254" s="11" t="s">
+        <v>625</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="C254" s="5">
+        <v>46316</v>
+      </c>
       <c r="D254" s="6"/>
       <c r="E254" s="6"/>
       <c r="F254" s="6"/>
@@ -13213,10 +14395,16 @@
       <c r="Y254" s="6"/>
       <c r="Z254" s="6"/>
     </row>
-    <row r="255" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A255" s="6"/>
-      <c r="B255" s="6"/>
-      <c r="C255" s="6"/>
+    <row r="255" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A255" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="C255" s="5">
+        <v>46317</v>
+      </c>
       <c r="D255" s="6"/>
       <c r="E255" s="6"/>
       <c r="F255" s="6"/>
@@ -13241,10 +14429,16 @@
       <c r="Y255" s="6"/>
       <c r="Z255" s="6"/>
     </row>
-    <row r="256" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A256" s="6"/>
-      <c r="B256" s="6"/>
-      <c r="C256" s="6"/>
+    <row r="256" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A256" s="11" t="s">
+        <v>627</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="C256" s="5">
+        <v>46318</v>
+      </c>
       <c r="D256" s="6"/>
       <c r="E256" s="6"/>
       <c r="F256" s="6"/>
@@ -13269,10 +14463,16 @@
       <c r="Y256" s="6"/>
       <c r="Z256" s="6"/>
     </row>
-    <row r="257" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A257" s="6"/>
-      <c r="B257" s="6"/>
-      <c r="C257" s="6"/>
+    <row r="257" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="11" t="s">
+        <v>628</v>
+      </c>
+      <c r="B257" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="C257" s="5">
+        <v>46319</v>
+      </c>
       <c r="D257" s="6"/>
       <c r="E257" s="6"/>
       <c r="F257" s="6"/>
@@ -13297,10 +14497,16 @@
       <c r="Y257" s="6"/>
       <c r="Z257" s="6"/>
     </row>
-    <row r="258" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A258" s="6"/>
-      <c r="B258" s="6"/>
-      <c r="C258" s="6"/>
+    <row r="258" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A258" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="C258" s="5">
+        <v>46320</v>
+      </c>
       <c r="D258" s="6"/>
       <c r="E258" s="6"/>
       <c r="F258" s="6"/>
@@ -13325,10 +14531,16 @@
       <c r="Y258" s="6"/>
       <c r="Z258" s="6"/>
     </row>
-    <row r="259" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A259" s="6"/>
-      <c r="B259" s="6"/>
-      <c r="C259" s="6"/>
+    <row r="259" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="C259" s="5">
+        <v>46321</v>
+      </c>
       <c r="D259" s="6"/>
       <c r="E259" s="6"/>
       <c r="F259" s="6"/>
@@ -13353,10 +14565,16 @@
       <c r="Y259" s="6"/>
       <c r="Z259" s="6"/>
     </row>
-    <row r="260" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A260" s="6"/>
-      <c r="B260" s="6"/>
-      <c r="C260" s="6"/>
+    <row r="260" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A260" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="B260" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="C260" s="5">
+        <v>46322</v>
+      </c>
       <c r="D260" s="6"/>
       <c r="E260" s="6"/>
       <c r="F260" s="6"/>
@@ -13381,10 +14599,16 @@
       <c r="Y260" s="6"/>
       <c r="Z260" s="6"/>
     </row>
-    <row r="261" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A261" s="6"/>
-      <c r="B261" s="6"/>
-      <c r="C261" s="6"/>
+    <row r="261" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A261" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="B261" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="C261" s="5">
+        <v>46323</v>
+      </c>
       <c r="D261" s="6"/>
       <c r="E261" s="6"/>
       <c r="F261" s="6"/>
@@ -13409,10 +14633,16 @@
       <c r="Y261" s="6"/>
       <c r="Z261" s="6"/>
     </row>
-    <row r="262" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A262" s="6"/>
-      <c r="B262" s="6"/>
-      <c r="C262" s="6"/>
+    <row r="262" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A262" s="11" t="s">
+        <v>632</v>
+      </c>
+      <c r="B262" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="C262" s="5">
+        <v>46324</v>
+      </c>
       <c r="D262" s="6"/>
       <c r="E262" s="6"/>
       <c r="F262" s="6"/>
@@ -13437,10 +14667,16 @@
       <c r="Y262" s="6"/>
       <c r="Z262" s="6"/>
     </row>
-    <row r="263" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A263" s="6"/>
-      <c r="B263" s="6"/>
-      <c r="C263" s="6"/>
+    <row r="263" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A263" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="B263" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="C263" s="5">
+        <v>46325</v>
+      </c>
       <c r="D263" s="6"/>
       <c r="E263" s="6"/>
       <c r="F263" s="6"/>
@@ -13465,10 +14701,16 @@
       <c r="Y263" s="6"/>
       <c r="Z263" s="6"/>
     </row>
-    <row r="264" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A264" s="6"/>
-      <c r="B264" s="6"/>
-      <c r="C264" s="6"/>
+    <row r="264" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A264" s="11" t="s">
+        <v>634</v>
+      </c>
+      <c r="B264" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="C264" s="5">
+        <v>46326</v>
+      </c>
       <c r="D264" s="6"/>
       <c r="E264" s="6"/>
       <c r="F264" s="6"/>
@@ -13493,10 +14735,16 @@
       <c r="Y264" s="6"/>
       <c r="Z264" s="6"/>
     </row>
-    <row r="265" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A265" s="6"/>
-      <c r="B265" s="6"/>
-      <c r="C265" s="6"/>
+    <row r="265" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A265" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="B265" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="C265" s="5">
+        <v>46327</v>
+      </c>
       <c r="D265" s="6"/>
       <c r="E265" s="6"/>
       <c r="F265" s="6"/>
@@ -13521,10 +14769,16 @@
       <c r="Y265" s="6"/>
       <c r="Z265" s="6"/>
     </row>
-    <row r="266" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A266" s="6"/>
-      <c r="B266" s="6"/>
-      <c r="C266" s="6"/>
+    <row r="266" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A266" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="B266" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="C266" s="5">
+        <v>46328</v>
+      </c>
       <c r="D266" s="6"/>
       <c r="E266" s="6"/>
       <c r="F266" s="6"/>
@@ -13549,10 +14803,16 @@
       <c r="Y266" s="6"/>
       <c r="Z266" s="6"/>
     </row>
-    <row r="267" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A267" s="6"/>
-      <c r="B267" s="6"/>
-      <c r="C267" s="6"/>
+    <row r="267" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A267" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="B267" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="C267" s="5">
+        <v>46329</v>
+      </c>
       <c r="D267" s="6"/>
       <c r="E267" s="6"/>
       <c r="F267" s="6"/>
@@ -13577,10 +14837,16 @@
       <c r="Y267" s="6"/>
       <c r="Z267" s="6"/>
     </row>
-    <row r="268" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A268" s="6"/>
-      <c r="B268" s="6"/>
-      <c r="C268" s="6"/>
+    <row r="268" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A268" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="B268" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="C268" s="5">
+        <v>46330</v>
+      </c>
       <c r="D268" s="6"/>
       <c r="E268" s="6"/>
       <c r="F268" s="6"/>
@@ -13605,10 +14871,16 @@
       <c r="Y268" s="6"/>
       <c r="Z268" s="6"/>
     </row>
-    <row r="269" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A269" s="6"/>
-      <c r="B269" s="6"/>
-      <c r="C269" s="6"/>
+    <row r="269" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A269" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="B269" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="C269" s="5">
+        <v>46331</v>
+      </c>
       <c r="D269" s="6"/>
       <c r="E269" s="6"/>
       <c r="F269" s="6"/>
@@ -13633,10 +14905,16 @@
       <c r="Y269" s="6"/>
       <c r="Z269" s="6"/>
     </row>
-    <row r="270" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A270" s="6"/>
-      <c r="B270" s="6"/>
-      <c r="C270" s="6"/>
+    <row r="270" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A270" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="B270" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="C270" s="5">
+        <v>46332</v>
+      </c>
       <c r="D270" s="6"/>
       <c r="E270" s="6"/>
       <c r="F270" s="6"/>
@@ -13661,10 +14939,16 @@
       <c r="Y270" s="6"/>
       <c r="Z270" s="6"/>
     </row>
-    <row r="271" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A271" s="6"/>
-      <c r="B271" s="6"/>
-      <c r="C271" s="6"/>
+    <row r="271" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A271" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="B271" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="C271" s="5">
+        <v>46333</v>
+      </c>
       <c r="D271" s="6"/>
       <c r="E271" s="6"/>
       <c r="F271" s="6"/>
@@ -13689,10 +14973,16 @@
       <c r="Y271" s="6"/>
       <c r="Z271" s="6"/>
     </row>
-    <row r="272" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A272" s="6"/>
-      <c r="B272" s="6"/>
-      <c r="C272" s="6"/>
+    <row r="272" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A272" s="11" t="s">
+        <v>642</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="C272" s="5">
+        <v>46334</v>
+      </c>
       <c r="D272" s="6"/>
       <c r="E272" s="6"/>
       <c r="F272" s="6"/>
@@ -13717,10 +15007,16 @@
       <c r="Y272" s="6"/>
       <c r="Z272" s="6"/>
     </row>
-    <row r="273" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A273" s="6"/>
-      <c r="B273" s="6"/>
-      <c r="C273" s="6"/>
+    <row r="273" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A273" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="B273" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="C273" s="5">
+        <v>46335</v>
+      </c>
       <c r="D273" s="6"/>
       <c r="E273" s="6"/>
       <c r="F273" s="6"/>
@@ -13745,10 +15041,16 @@
       <c r="Y273" s="6"/>
       <c r="Z273" s="6"/>
     </row>
-    <row r="274" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A274" s="6"/>
-      <c r="B274" s="6"/>
-      <c r="C274" s="6"/>
+    <row r="274" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A274" s="11" t="s">
+        <v>643</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="C274" s="5">
+        <v>46336</v>
+      </c>
       <c r="D274" s="6"/>
       <c r="E274" s="6"/>
       <c r="F274" s="6"/>
@@ -13773,10 +15075,16 @@
       <c r="Y274" s="6"/>
       <c r="Z274" s="6"/>
     </row>
-    <row r="275" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A275" s="6"/>
-      <c r="B275" s="6"/>
-      <c r="C275" s="6"/>
+    <row r="275" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A275" s="11" t="s">
+        <v>644</v>
+      </c>
+      <c r="B275" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="C275" s="5">
+        <v>46337</v>
+      </c>
       <c r="D275" s="6"/>
       <c r="E275" s="6"/>
       <c r="F275" s="6"/>
@@ -13801,10 +15109,16 @@
       <c r="Y275" s="6"/>
       <c r="Z275" s="6"/>
     </row>
-    <row r="276" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A276" s="6"/>
-      <c r="B276" s="6"/>
-      <c r="C276" s="6"/>
+    <row r="276" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A276" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="C276" s="5">
+        <v>46338</v>
+      </c>
       <c r="D276" s="6"/>
       <c r="E276" s="6"/>
       <c r="F276" s="6"/>
@@ -13829,10 +15143,16 @@
       <c r="Y276" s="6"/>
       <c r="Z276" s="6"/>
     </row>
-    <row r="277" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A277" s="6"/>
-      <c r="B277" s="6"/>
-      <c r="C277" s="6"/>
+    <row r="277" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A277" s="11" t="s">
+        <v>646</v>
+      </c>
+      <c r="B277" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="C277" s="5">
+        <v>46339</v>
+      </c>
       <c r="D277" s="6"/>
       <c r="E277" s="6"/>
       <c r="F277" s="6"/>
@@ -13857,10 +15177,16 @@
       <c r="Y277" s="6"/>
       <c r="Z277" s="6"/>
     </row>
-    <row r="278" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A278" s="6"/>
-      <c r="B278" s="6"/>
-      <c r="C278" s="6"/>
+    <row r="278" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A278" s="11" t="s">
+        <v>647</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="C278" s="5">
+        <v>46340</v>
+      </c>
       <c r="D278" s="6"/>
       <c r="E278" s="6"/>
       <c r="F278" s="6"/>
@@ -13885,10 +15211,16 @@
       <c r="Y278" s="6"/>
       <c r="Z278" s="6"/>
     </row>
-    <row r="279" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A279" s="6"/>
-      <c r="B279" s="6"/>
-      <c r="C279" s="6"/>
+    <row r="279" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A279" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="C279" s="5">
+        <v>46341</v>
+      </c>
       <c r="D279" s="6"/>
       <c r="E279" s="6"/>
       <c r="F279" s="6"/>
@@ -13913,10 +15245,16 @@
       <c r="Y279" s="6"/>
       <c r="Z279" s="6"/>
     </row>
-    <row r="280" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A280" s="6"/>
-      <c r="B280" s="6"/>
-      <c r="C280" s="6"/>
+    <row r="280" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A280" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="C280" s="5">
+        <v>46342</v>
+      </c>
       <c r="D280" s="6"/>
       <c r="E280" s="6"/>
       <c r="F280" s="6"/>
@@ -13941,10 +15279,16 @@
       <c r="Y280" s="6"/>
       <c r="Z280" s="6"/>
     </row>
-    <row r="281" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A281" s="6"/>
-      <c r="B281" s="6"/>
-      <c r="C281" s="6"/>
+    <row r="281" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A281" s="11" t="s">
+        <v>649</v>
+      </c>
+      <c r="B281" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="C281" s="5">
+        <v>46343</v>
+      </c>
       <c r="D281" s="6"/>
       <c r="E281" s="6"/>
       <c r="F281" s="6"/>
@@ -13969,10 +15313,16 @@
       <c r="Y281" s="6"/>
       <c r="Z281" s="6"/>
     </row>
-    <row r="282" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A282" s="6"/>
-      <c r="B282" s="6"/>
-      <c r="C282" s="6"/>
+    <row r="282" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A282" s="11" t="s">
+        <v>650</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="C282" s="5">
+        <v>46344</v>
+      </c>
       <c r="D282" s="6"/>
       <c r="E282" s="6"/>
       <c r="F282" s="6"/>
@@ -13997,10 +15347,16 @@
       <c r="Y282" s="6"/>
       <c r="Z282" s="6"/>
     </row>
-    <row r="283" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A283" s="6"/>
-      <c r="B283" s="6"/>
-      <c r="C283" s="6"/>
+    <row r="283" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A283" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="C283" s="5">
+        <v>46345</v>
+      </c>
       <c r="D283" s="6"/>
       <c r="E283" s="6"/>
       <c r="F283" s="6"/>
@@ -14025,10 +15381,16 @@
       <c r="Y283" s="6"/>
       <c r="Z283" s="6"/>
     </row>
-    <row r="284" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A284" s="6"/>
-      <c r="B284" s="6"/>
-      <c r="C284" s="6"/>
+    <row r="284" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A284" s="11" t="s">
+        <v>652</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="C284" s="5">
+        <v>46346</v>
+      </c>
       <c r="D284" s="6"/>
       <c r="E284" s="6"/>
       <c r="F284" s="6"/>
@@ -14053,10 +15415,16 @@
       <c r="Y284" s="6"/>
       <c r="Z284" s="6"/>
     </row>
-    <row r="285" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A285" s="6"/>
-      <c r="B285" s="6"/>
-      <c r="C285" s="6"/>
+    <row r="285" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A285" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="C285" s="5">
+        <v>46347</v>
+      </c>
       <c r="D285" s="6"/>
       <c r="E285" s="6"/>
       <c r="F285" s="6"/>
@@ -14081,10 +15449,16 @@
       <c r="Y285" s="6"/>
       <c r="Z285" s="6"/>
     </row>
-    <row r="286" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A286" s="6"/>
-      <c r="B286" s="6"/>
-      <c r="C286" s="6"/>
+    <row r="286" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A286" s="11" t="s">
+        <v>654</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="C286" s="5">
+        <v>46348</v>
+      </c>
       <c r="D286" s="6"/>
       <c r="E286" s="6"/>
       <c r="F286" s="6"/>
@@ -14109,10 +15483,16 @@
       <c r="Y286" s="6"/>
       <c r="Z286" s="6"/>
     </row>
-    <row r="287" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A287" s="6"/>
-      <c r="B287" s="6"/>
-      <c r="C287" s="6"/>
+    <row r="287" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A287" s="11" t="s">
+        <v>655</v>
+      </c>
+      <c r="B287" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="C287" s="5">
+        <v>46349</v>
+      </c>
       <c r="D287" s="6"/>
       <c r="E287" s="6"/>
       <c r="F287" s="6"/>
@@ -14137,10 +15517,16 @@
       <c r="Y287" s="6"/>
       <c r="Z287" s="6"/>
     </row>
-    <row r="288" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A288" s="6"/>
-      <c r="B288" s="6"/>
-      <c r="C288" s="6"/>
+    <row r="288" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A288" s="11" t="s">
+        <v>656</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="C288" s="5">
+        <v>46350</v>
+      </c>
       <c r="D288" s="6"/>
       <c r="E288" s="6"/>
       <c r="F288" s="6"/>
@@ -14165,10 +15551,16 @@
       <c r="Y288" s="6"/>
       <c r="Z288" s="6"/>
     </row>
-    <row r="289" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A289" s="6"/>
-      <c r="B289" s="6"/>
-      <c r="C289" s="6"/>
+    <row r="289" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A289" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="C289" s="5">
+        <v>46351</v>
+      </c>
       <c r="D289" s="6"/>
       <c r="E289" s="6"/>
       <c r="F289" s="6"/>
@@ -14193,10 +15585,16 @@
       <c r="Y289" s="6"/>
       <c r="Z289" s="6"/>
     </row>
-    <row r="290" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A290" s="6"/>
-      <c r="B290" s="6"/>
-      <c r="C290" s="6"/>
+    <row r="290" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A290" s="11" t="s">
+        <v>658</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="C290" s="5">
+        <v>46352</v>
+      </c>
       <c r="D290" s="6"/>
       <c r="E290" s="6"/>
       <c r="F290" s="6"/>
@@ -14221,10 +15619,16 @@
       <c r="Y290" s="6"/>
       <c r="Z290" s="6"/>
     </row>
-    <row r="291" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A291" s="6"/>
-      <c r="B291" s="6"/>
-      <c r="C291" s="6"/>
+    <row r="291" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A291" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="C291" s="5">
+        <v>46353</v>
+      </c>
       <c r="D291" s="6"/>
       <c r="E291" s="6"/>
       <c r="F291" s="6"/>
@@ -14249,10 +15653,16 @@
       <c r="Y291" s="6"/>
       <c r="Z291" s="6"/>
     </row>
-    <row r="292" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A292" s="6"/>
-      <c r="B292" s="6"/>
-      <c r="C292" s="6"/>
+    <row r="292" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A292" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="C292" s="5">
+        <v>46354</v>
+      </c>
       <c r="D292" s="6"/>
       <c r="E292" s="6"/>
       <c r="F292" s="6"/>
@@ -14277,10 +15687,16 @@
       <c r="Y292" s="6"/>
       <c r="Z292" s="6"/>
     </row>
-    <row r="293" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A293" s="6"/>
-      <c r="B293" s="6"/>
-      <c r="C293" s="6"/>
+    <row r="293" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A293" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>670</v>
+      </c>
+      <c r="C293" s="5">
+        <v>46355</v>
+      </c>
       <c r="D293" s="6"/>
       <c r="E293" s="6"/>
       <c r="F293" s="6"/>
@@ -14305,10 +15721,16 @@
       <c r="Y293" s="6"/>
       <c r="Z293" s="6"/>
     </row>
-    <row r="294" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A294" s="6"/>
-      <c r="B294" s="6"/>
-      <c r="C294" s="6"/>
+    <row r="294" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A294" s="11" t="s">
+        <v>662</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="C294" s="5">
+        <v>46356</v>
+      </c>
       <c r="D294" s="6"/>
       <c r="E294" s="6"/>
       <c r="F294" s="6"/>
@@ -14333,10 +15755,16 @@
       <c r="Y294" s="6"/>
       <c r="Z294" s="6"/>
     </row>
-    <row r="295" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A295" s="6"/>
-      <c r="B295" s="6"/>
-      <c r="C295" s="6"/>
+    <row r="295" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A295" s="11" t="s">
+        <v>663</v>
+      </c>
+      <c r="B295" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="C295" s="5">
+        <v>46357</v>
+      </c>
       <c r="D295" s="6"/>
       <c r="E295" s="6"/>
       <c r="F295" s="6"/>
@@ -14361,10 +15789,16 @@
       <c r="Y295" s="6"/>
       <c r="Z295" s="6"/>
     </row>
-    <row r="296" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A296" s="6"/>
-      <c r="B296" s="6"/>
-      <c r="C296" s="6"/>
+    <row r="296" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A296" s="11" t="s">
+        <v>664</v>
+      </c>
+      <c r="B296" s="6" t="s">
+        <v>673</v>
+      </c>
+      <c r="C296" s="5">
+        <v>46358</v>
+      </c>
       <c r="D296" s="6"/>
       <c r="E296" s="6"/>
       <c r="F296" s="6"/>
@@ -14389,10 +15823,16 @@
       <c r="Y296" s="6"/>
       <c r="Z296" s="6"/>
     </row>
-    <row r="297" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A297" s="6"/>
-      <c r="B297" s="6"/>
-      <c r="C297" s="6"/>
+    <row r="297" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A297" s="11" t="s">
+        <v>665</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>674</v>
+      </c>
+      <c r="C297" s="5">
+        <v>46359</v>
+      </c>
       <c r="D297" s="6"/>
       <c r="E297" s="6"/>
       <c r="F297" s="6"/>
@@ -14417,10 +15857,16 @@
       <c r="Y297" s="6"/>
       <c r="Z297" s="6"/>
     </row>
-    <row r="298" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A298" s="6"/>
-      <c r="B298" s="6"/>
-      <c r="C298" s="6"/>
+    <row r="298" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A298" s="11" t="s">
+        <v>666</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="C298" s="5">
+        <v>46360</v>
+      </c>
       <c r="D298" s="6"/>
       <c r="E298" s="6"/>
       <c r="F298" s="6"/>
@@ -14445,10 +15891,16 @@
       <c r="Y298" s="6"/>
       <c r="Z298" s="6"/>
     </row>
-    <row r="299" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A299" s="6"/>
-      <c r="B299" s="6"/>
-      <c r="C299" s="6"/>
+    <row r="299" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A299" s="11" t="s">
+        <v>667</v>
+      </c>
+      <c r="B299" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="C299" s="5">
+        <v>46361</v>
+      </c>
       <c r="D299" s="6"/>
       <c r="E299" s="6"/>
       <c r="F299" s="6"/>
@@ -32857,9 +34309,70 @@
     <hyperlink ref="A236" r:id="rId235" display="https://www.youtube.com/watch?v=7rdJOSgHgg4&amp;t=559s" xr:uid="{01909B77-657A-491C-B14B-54B0CAC58311}"/>
     <hyperlink ref="A237" r:id="rId236" xr:uid="{5A1B9525-3FD4-4576-B6C2-C275598276F5}"/>
     <hyperlink ref="A238" r:id="rId237" display="https://www.youtube.com/watch?v=tS58CDMrFxA&amp;t=23s" xr:uid="{8BDBC4D2-1AEC-4538-A0AB-264071C82E94}"/>
+    <hyperlink ref="A239" r:id="rId238" xr:uid="{6B92B725-BC0F-475E-9F65-16333A3F9365}"/>
+    <hyperlink ref="A240" r:id="rId239" display="https://www.youtube.com/watch?v=iT7CUPzFbRQ&amp;t=9s" xr:uid="{E4BE9646-7B59-4AD7-A24A-270D83646497}"/>
+    <hyperlink ref="A241" r:id="rId240" display="https://www.youtube.com/watch?v=vuSYcVsLKhY&amp;t=1531s" xr:uid="{5539C85D-B4CF-476E-9D1C-340982C76790}"/>
+    <hyperlink ref="A242" r:id="rId241" display="https://www.youtube.com/watch?v=MJsviZtSPFc&amp;t=12s" xr:uid="{6B007E1D-4F1A-471F-BFB9-B285A5D856C4}"/>
+    <hyperlink ref="A243" r:id="rId242" display="https://www.youtube.com/watch?v=Ya86jfgQxPU&amp;t=49s" xr:uid="{4B555E75-6CDC-442E-ABCC-D8F0EC64F6F1}"/>
+    <hyperlink ref="A244" r:id="rId243" display="https://www.youtube.com/watch?v=jJSRiLY_hKo&amp;t=2s" xr:uid="{E36E4F0E-735F-4959-9001-CFD90CE51078}"/>
+    <hyperlink ref="A245" r:id="rId244" display="https://www.youtube.com/watch?v=-NHHdVWUcwo&amp;t=2s" xr:uid="{03A0E9E7-4B11-460C-B7BB-8A45AE603B6B}"/>
+    <hyperlink ref="A246" r:id="rId245" display="https://www.youtube.com/watch?v=1fPXxQTCPKQ&amp;t=1s" xr:uid="{D3E32417-2661-4289-B099-18CF8929D5E6}"/>
+    <hyperlink ref="A247" r:id="rId246" xr:uid="{52C9B898-C381-40FB-9E89-324F5ACA03FD}"/>
+    <hyperlink ref="A248" r:id="rId247" xr:uid="{F9FB9359-1866-467F-AD00-C180A65850EE}"/>
+    <hyperlink ref="A249" r:id="rId248" xr:uid="{0CF84BB7-1A1E-4060-9D12-F3733FD23931}"/>
+    <hyperlink ref="A250" r:id="rId249" xr:uid="{8F961645-09D9-4152-8CFB-E7A34B07857B}"/>
+    <hyperlink ref="A251" r:id="rId250" display="https://www.youtube.com/watch?v=G3QwYAUfSQY&amp;t=3s" xr:uid="{090C9BB6-3566-4C90-BDD0-651B9BDFE49A}"/>
+    <hyperlink ref="A252" r:id="rId251" display="https://www.youtube.com/watch?v=3OuM3M9TXkg&amp;t=1s" xr:uid="{21F6EEBF-990E-4675-A20A-C891D57E1B8C}"/>
+    <hyperlink ref="A253" r:id="rId252" xr:uid="{9ED15BAF-BA39-4FB9-AB6B-B7A1CEFB5F6D}"/>
+    <hyperlink ref="A254" r:id="rId253" display="https://www.youtube.com/watch?v=XDoquCuFKGk&amp;t=242s" xr:uid="{D855E543-128F-4B8E-B304-B165E8D4B779}"/>
+    <hyperlink ref="A255" r:id="rId254" display="https://www.youtube.com/watch?v=qYqJ9IOnwBY&amp;t=47s" xr:uid="{ACB4C38C-DCE4-498C-98EB-33DCED92D73E}"/>
+    <hyperlink ref="A256" r:id="rId255" xr:uid="{FF02D5D8-9045-47F4-A46C-D74536914157}"/>
+    <hyperlink ref="A257" r:id="rId256" display="https://www.youtube.com/watch?v=Ne58ALWRs68&amp;t=46s" xr:uid="{F9AFE816-C163-44DC-905E-C4B2913A8AD3}"/>
+    <hyperlink ref="A258" r:id="rId257" display="https://www.youtube.com/watch?v=hE9f3FTjhog&amp;t=28s" xr:uid="{465DD0D1-73BE-4A66-85F7-CF9ACA00585D}"/>
+    <hyperlink ref="A259" r:id="rId258" xr:uid="{EC99A6FD-60F7-46DA-B226-93A2CFA33C86}"/>
+    <hyperlink ref="A260" r:id="rId259" display="https://www.youtube.com/watch?v=8siMw00cRt8&amp;t=1s" xr:uid="{D9462382-0519-470D-B1C3-3FCC75DAEDA8}"/>
+    <hyperlink ref="A261" r:id="rId260" display="https://www.youtube.com/watch?v=Q24FZ2FRwGQ&amp;t=2s" xr:uid="{4BA34863-4AEC-4941-85FE-A56901B91721}"/>
+    <hyperlink ref="A262" r:id="rId261" xr:uid="{B2301D43-2EC7-4412-BC51-C06F2ABEF1C0}"/>
+    <hyperlink ref="A263" r:id="rId262" display="https://www.youtube.com/watch?v=GTeBLRi-Hho&amp;t=1s" xr:uid="{B478CF7A-EB2E-4644-AAC5-47F11E03D7AA}"/>
+    <hyperlink ref="A264" r:id="rId263" display="https://www.youtube.com/watch?v=AW19y7ztyKs&amp;t=1361s" xr:uid="{AE6DDED5-82EE-49D8-B30B-B6E40B746408}"/>
+    <hyperlink ref="A265" r:id="rId264" display="https://www.youtube.com/watch?v=nbGi3a_tyi0&amp;t=2s" xr:uid="{E9786154-329F-489D-BBC0-C763975EC0A9}"/>
+    <hyperlink ref="A266" r:id="rId265" display="https://www.youtube.com/watch?v=QqTdOn-fxO4&amp;t=18s" xr:uid="{CEC9CA11-5B90-4846-AEBF-8DB891561908}"/>
+    <hyperlink ref="A267" r:id="rId266" display="https://www.youtube.com/watch?v=z2dGDx3u5p0&amp;t=232s" xr:uid="{7261A18E-9C7C-4DB2-886C-9CC59C0B8E06}"/>
+    <hyperlink ref="A268" r:id="rId267" display="https://www.youtube.com/watch?v=rPfM-T7cae8&amp;t=1s" xr:uid="{8050135E-7559-441F-9AF7-6796F05DF4EE}"/>
+    <hyperlink ref="A269" r:id="rId268" xr:uid="{0AE6E7FF-5990-4741-A8CA-0C68FEDFE6A3}"/>
+    <hyperlink ref="A270" r:id="rId269" display="https://www.youtube.com/watch?v=HLgoQEBcm6o&amp;t=125s" xr:uid="{4BA73466-6A30-4E30-A258-B705E196F95F}"/>
+    <hyperlink ref="A271" r:id="rId270" display="https://www.youtube.com/watch?v=ruWNJ2f_KJs&amp;t=16s" xr:uid="{167CFCB8-C2E5-4F68-BFDE-B7A08F02A697}"/>
+    <hyperlink ref="A272" r:id="rId271" xr:uid="{6CD68787-14A1-42CB-B8AC-CE48398FDB06}"/>
+    <hyperlink ref="A273" r:id="rId272" display="https://www.youtube.com/watch?v=ixeML2iYD3w&amp;t=3s" xr:uid="{2E87F204-81B7-44B8-9AB6-0F8CD4304B63}"/>
+    <hyperlink ref="A274" r:id="rId273" xr:uid="{1F40B6FE-9A31-4432-BFBF-C59D4EFAA8A2}"/>
+    <hyperlink ref="A275" r:id="rId274" display="https://www.youtube.com/watch?v=Lxwh9fSrLfo&amp;t=4s" xr:uid="{9F805BA2-FA44-49A2-8632-574E2D09E8A4}"/>
+    <hyperlink ref="A276" r:id="rId275" xr:uid="{7549E620-9261-4C6B-BCC6-AF5B6389E2C5}"/>
+    <hyperlink ref="A277" r:id="rId276" display="https://www.youtube.com/watch?v=Yjc7P_-Yuhg&amp;t=42s" xr:uid="{042398D1-F33D-4B6F-8A5A-468FFAEECAF5}"/>
+    <hyperlink ref="A278" r:id="rId277" display="https://www.youtube.com/watch?v=Mv14PuzubPs&amp;t=2s" xr:uid="{7C46DC17-C9E6-4CB7-8946-4A9F5D85D6C1}"/>
+    <hyperlink ref="A279" r:id="rId278" display="https://www.youtube.com/watch?v=vVvHXSohHwA&amp;t=4s" xr:uid="{8B647792-5B8D-420B-8422-D21B2859482B}"/>
+    <hyperlink ref="A280" r:id="rId279" display="https://www.youtube.com/watch?v=vVvHXSohHwA&amp;t=4s" xr:uid="{DAA694E2-FE70-4779-A89E-3235E59D2A99}"/>
+    <hyperlink ref="A281" r:id="rId280" xr:uid="{A63A4AE6-3B6D-4E7B-BCA4-E4C4E4A6657F}"/>
+    <hyperlink ref="A282" r:id="rId281" display="https://www.youtube.com/watch?v=TLaRnmjmabE&amp;t=2s" xr:uid="{ADA5F744-E07C-4ED2-8EC0-39983BEF7673}"/>
+    <hyperlink ref="A283" r:id="rId282" display="https://www.youtube.com/watch?v=8LGfGpiD-Mk&amp;t=11s" xr:uid="{EE7BB1E0-F077-4120-BAA0-D50B8DD12721}"/>
+    <hyperlink ref="A284" r:id="rId283" display="https://www.youtube.com/watch?v=NrBla1RTvTE&amp;t=29s" xr:uid="{DF2A6F01-484F-45C7-A5B5-462CA48992CE}"/>
+    <hyperlink ref="A285" r:id="rId284" xr:uid="{F01E5F64-AEDF-4819-863F-C868736863FA}"/>
+    <hyperlink ref="A286" r:id="rId285" xr:uid="{A337BEE7-364A-4CE9-BA44-C0B7FD78A219}"/>
+    <hyperlink ref="A287" r:id="rId286" xr:uid="{8C157E1F-7B40-436B-9B72-DF6E3F5D5BF2}"/>
+    <hyperlink ref="A288" r:id="rId287" xr:uid="{00574920-A530-41F6-8742-107CFEA9FC19}"/>
+    <hyperlink ref="A289" r:id="rId288" display="https://www.youtube.com/watch?v=Ai0jdNcEMHw&amp;t=5s" xr:uid="{6CA90576-4B14-4193-849F-456E3A5D627D}"/>
+    <hyperlink ref="A290" r:id="rId289" xr:uid="{9B9B97AD-AD1E-41C9-996F-7D0689099246}"/>
+    <hyperlink ref="A291" r:id="rId290" xr:uid="{8061578D-9A15-4D3C-B25D-72A7AA6EFC34}"/>
+    <hyperlink ref="A292" r:id="rId291" xr:uid="{A2F43D3C-BCD9-40FA-A76B-559F503428BB}"/>
+    <hyperlink ref="A293" r:id="rId292" xr:uid="{23B3BBFA-2541-4A72-B0F3-B0EBEB760B59}"/>
+    <hyperlink ref="A294" r:id="rId293" xr:uid="{34D19071-A866-4643-A70C-BDB8FD864E10}"/>
+    <hyperlink ref="A295" r:id="rId294" xr:uid="{9599EE20-BD9A-4F36-B0C8-99929591CCC9}"/>
+    <hyperlink ref="A296" r:id="rId295" xr:uid="{1C21AD91-091D-4FA5-8E2A-4113073A196C}"/>
+    <hyperlink ref="A297" r:id="rId296" xr:uid="{2E66E85D-2839-4A26-8194-432975438BD0}"/>
+    <hyperlink ref="A298" r:id="rId297" xr:uid="{F21E73D3-2642-4F99-B5A8-60E30C0F92FD}"/>
+    <hyperlink ref="A299" r:id="rId298" xr:uid="{4E4E6C59-E68A-4009-A885-D9398AA38E2E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId238"/>
+  <pageSetup orientation="portrait" r:id="rId299"/>
 </worksheet>
 </file>
 
@@ -39711,10 +41224,16 @@
       <c r="Y201" s="6"/>
       <c r="Z201" s="6"/>
     </row>
-    <row r="202" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A202" s="6"/>
-      <c r="B202" s="6"/>
-      <c r="C202" s="8"/>
+    <row r="202" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="C202" s="7">
+        <v>46301</v>
+      </c>
       <c r="D202" s="6"/>
       <c r="E202" s="6"/>
       <c r="F202" s="6"/>
@@ -39739,10 +41258,16 @@
       <c r="Y202" s="6"/>
       <c r="Z202" s="6"/>
     </row>
-    <row r="203" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A203" s="6"/>
-      <c r="B203" s="6"/>
-      <c r="C203" s="8"/>
+    <row r="203" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="11" t="s">
+        <v>612</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="C203" s="7">
+        <v>46302</v>
+      </c>
       <c r="D203" s="6"/>
       <c r="E203" s="6"/>
       <c r="F203" s="6"/>
@@ -39767,10 +41292,16 @@
       <c r="Y203" s="6"/>
       <c r="Z203" s="6"/>
     </row>
-    <row r="204" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A204" s="6"/>
-      <c r="B204" s="6"/>
-      <c r="C204" s="8"/>
+    <row r="204" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="C204" s="7">
+        <v>46303</v>
+      </c>
       <c r="D204" s="6"/>
       <c r="E204" s="6"/>
       <c r="F204" s="6"/>
@@ -39795,10 +41326,16 @@
       <c r="Y204" s="6"/>
       <c r="Z204" s="6"/>
     </row>
-    <row r="205" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A205" s="6"/>
-      <c r="B205" s="6"/>
-      <c r="C205" s="8"/>
+    <row r="205" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="11" t="s">
+        <v>614</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C205" s="7">
+        <v>46304</v>
+      </c>
       <c r="D205" s="6"/>
       <c r="E205" s="6"/>
       <c r="F205" s="6"/>
@@ -39823,10 +41360,16 @@
       <c r="Y205" s="6"/>
       <c r="Z205" s="6"/>
     </row>
-    <row r="206" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A206" s="6"/>
-      <c r="B206" s="6"/>
-      <c r="C206" s="8"/>
+    <row r="206" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="C206" s="7">
+        <v>46305</v>
+      </c>
       <c r="D206" s="6"/>
       <c r="E206" s="6"/>
       <c r="F206" s="6"/>
@@ -39851,10 +41394,16 @@
       <c r="Y206" s="6"/>
       <c r="Z206" s="6"/>
     </row>
-    <row r="207" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A207" s="6"/>
-      <c r="B207" s="6"/>
-      <c r="C207" s="8"/>
+    <row r="207" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="C207" s="7">
+        <v>46306</v>
+      </c>
       <c r="D207" s="6"/>
       <c r="E207" s="6"/>
       <c r="F207" s="6"/>
@@ -39879,10 +41428,16 @@
       <c r="Y207" s="6"/>
       <c r="Z207" s="6"/>
     </row>
-    <row r="208" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A208" s="6"/>
-      <c r="B208" s="6"/>
-      <c r="C208" s="8"/>
+    <row r="208" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="C208" s="7">
+        <v>46307</v>
+      </c>
       <c r="D208" s="6"/>
       <c r="E208" s="6"/>
       <c r="F208" s="6"/>
@@ -39907,10 +41462,16 @@
       <c r="Y208" s="6"/>
       <c r="Z208" s="6"/>
     </row>
-    <row r="209" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A209" s="6"/>
-      <c r="B209" s="6"/>
-      <c r="C209" s="8"/>
+    <row r="209" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="11" t="s">
+        <v>617</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="C209" s="7">
+        <v>46308</v>
+      </c>
       <c r="D209" s="6"/>
       <c r="E209" s="6"/>
       <c r="F209" s="6"/>
@@ -39935,10 +41496,16 @@
       <c r="Y209" s="6"/>
       <c r="Z209" s="6"/>
     </row>
-    <row r="210" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A210" s="6"/>
-      <c r="B210" s="6"/>
-      <c r="C210" s="8"/>
+    <row r="210" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="11" t="s">
+        <v>618</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C210" s="7">
+        <v>46309</v>
+      </c>
       <c r="D210" s="6"/>
       <c r="E210" s="6"/>
       <c r="F210" s="6"/>
@@ -39963,10 +41530,16 @@
       <c r="Y210" s="6"/>
       <c r="Z210" s="6"/>
     </row>
-    <row r="211" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A211" s="6"/>
-      <c r="B211" s="6"/>
-      <c r="C211" s="8"/>
+    <row r="211" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="C211" s="7">
+        <v>46310</v>
+      </c>
       <c r="D211" s="6"/>
       <c r="E211" s="6"/>
       <c r="F211" s="6"/>
@@ -39991,10 +41564,16 @@
       <c r="Y211" s="6"/>
       <c r="Z211" s="6"/>
     </row>
-    <row r="212" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A212" s="6"/>
-      <c r="B212" s="6"/>
-      <c r="C212" s="8"/>
+    <row r="212" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C212" s="7">
+        <v>46311</v>
+      </c>
       <c r="D212" s="6"/>
       <c r="E212" s="6"/>
       <c r="F212" s="6"/>
@@ -40019,10 +41598,16 @@
       <c r="Y212" s="6"/>
       <c r="Z212" s="6"/>
     </row>
-    <row r="213" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A213" s="6"/>
-      <c r="B213" s="6"/>
-      <c r="C213" s="8"/>
+    <row r="213" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="11" t="s">
+        <v>621</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="C213" s="7">
+        <v>46312</v>
+      </c>
       <c r="D213" s="6"/>
       <c r="E213" s="6"/>
       <c r="F213" s="6"/>
@@ -40047,10 +41632,16 @@
       <c r="Y213" s="6"/>
       <c r="Z213" s="6"/>
     </row>
-    <row r="214" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A214" s="6"/>
-      <c r="B214" s="6"/>
-      <c r="C214" s="8"/>
+    <row r="214" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="11" t="s">
+        <v>622</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="C214" s="7">
+        <v>46313</v>
+      </c>
       <c r="D214" s="6"/>
       <c r="E214" s="6"/>
       <c r="F214" s="6"/>
@@ -40075,10 +41666,16 @@
       <c r="Y214" s="6"/>
       <c r="Z214" s="6"/>
     </row>
-    <row r="215" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A215" s="6"/>
-      <c r="B215" s="6"/>
-      <c r="C215" s="8"/>
+    <row r="215" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="11" t="s">
+        <v>623</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="C215" s="7">
+        <v>46314</v>
+      </c>
       <c r="D215" s="6"/>
       <c r="E215" s="6"/>
       <c r="F215" s="6"/>
@@ -40103,10 +41700,16 @@
       <c r="Y215" s="6"/>
       <c r="Z215" s="6"/>
     </row>
-    <row r="216" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A216" s="6"/>
-      <c r="B216" s="6"/>
-      <c r="C216" s="8"/>
+    <row r="216" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="11" t="s">
+        <v>624</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="C216" s="7">
+        <v>46315</v>
+      </c>
       <c r="D216" s="6"/>
       <c r="E216" s="6"/>
       <c r="F216" s="6"/>
@@ -40131,10 +41734,16 @@
       <c r="Y216" s="6"/>
       <c r="Z216" s="6"/>
     </row>
-    <row r="217" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A217" s="6"/>
-      <c r="B217" s="6"/>
-      <c r="C217" s="8"/>
+    <row r="217" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="11" t="s">
+        <v>625</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="C217" s="7">
+        <v>46316</v>
+      </c>
       <c r="D217" s="6"/>
       <c r="E217" s="6"/>
       <c r="F217" s="6"/>
@@ -40159,10 +41768,16 @@
       <c r="Y217" s="6"/>
       <c r="Z217" s="6"/>
     </row>
-    <row r="218" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A218" s="6"/>
-      <c r="B218" s="6"/>
-      <c r="C218" s="8"/>
+    <row r="218" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="C218" s="7">
+        <v>46317</v>
+      </c>
       <c r="D218" s="6"/>
       <c r="E218" s="6"/>
       <c r="F218" s="6"/>
@@ -40187,10 +41802,16 @@
       <c r="Y218" s="6"/>
       <c r="Z218" s="6"/>
     </row>
-    <row r="219" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A219" s="6"/>
-      <c r="B219" s="6"/>
-      <c r="C219" s="8"/>
+    <row r="219" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="11" t="s">
+        <v>627</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C219" s="7">
+        <v>46318</v>
+      </c>
       <c r="D219" s="6"/>
       <c r="E219" s="6"/>
       <c r="F219" s="6"/>
@@ -40215,10 +41836,16 @@
       <c r="Y219" s="6"/>
       <c r="Z219" s="6"/>
     </row>
-    <row r="220" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A220" s="6"/>
-      <c r="B220" s="6"/>
-      <c r="C220" s="8"/>
+    <row r="220" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A220" s="11" t="s">
+        <v>628</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="C220" s="7">
+        <v>46319</v>
+      </c>
       <c r="D220" s="6"/>
       <c r="E220" s="6"/>
       <c r="F220" s="6"/>
@@ -40243,10 +41870,16 @@
       <c r="Y220" s="6"/>
       <c r="Z220" s="6"/>
     </row>
-    <row r="221" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A221" s="6"/>
-      <c r="B221" s="6"/>
-      <c r="C221" s="8"/>
+    <row r="221" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A221" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="C221" s="7">
+        <v>46320</v>
+      </c>
       <c r="D221" s="6"/>
       <c r="E221" s="6"/>
       <c r="F221" s="6"/>
@@ -40271,10 +41904,16 @@
       <c r="Y221" s="6"/>
       <c r="Z221" s="6"/>
     </row>
-    <row r="222" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A222" s="6"/>
-      <c r="B222" s="6"/>
-      <c r="C222" s="8"/>
+    <row r="222" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A222" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="C222" s="7">
+        <v>46321</v>
+      </c>
       <c r="D222" s="6"/>
       <c r="E222" s="6"/>
       <c r="F222" s="6"/>
@@ -40299,10 +41938,16 @@
       <c r="Y222" s="6"/>
       <c r="Z222" s="6"/>
     </row>
-    <row r="223" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A223" s="6"/>
-      <c r="B223" s="6"/>
-      <c r="C223" s="8"/>
+    <row r="223" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A223" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="C223" s="7">
+        <v>46322</v>
+      </c>
       <c r="D223" s="6"/>
       <c r="E223" s="6"/>
       <c r="F223" s="6"/>
@@ -40327,10 +41972,16 @@
       <c r="Y223" s="6"/>
       <c r="Z223" s="6"/>
     </row>
-    <row r="224" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A224" s="6"/>
-      <c r="B224" s="6"/>
-      <c r="C224" s="8"/>
+    <row r="224" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A224" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="C224" s="7">
+        <v>46323</v>
+      </c>
       <c r="D224" s="6"/>
       <c r="E224" s="6"/>
       <c r="F224" s="6"/>
@@ -40355,10 +42006,16 @@
       <c r="Y224" s="6"/>
       <c r="Z224" s="6"/>
     </row>
-    <row r="225" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A225" s="6"/>
-      <c r="B225" s="6"/>
-      <c r="C225" s="8"/>
+    <row r="225" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="11" t="s">
+        <v>632</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C225" s="7">
+        <v>46324</v>
+      </c>
       <c r="D225" s="6"/>
       <c r="E225" s="6"/>
       <c r="F225" s="6"/>
@@ -40383,10 +42040,16 @@
       <c r="Y225" s="6"/>
       <c r="Z225" s="6"/>
     </row>
-    <row r="226" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A226" s="6"/>
-      <c r="B226" s="6"/>
-      <c r="C226" s="8"/>
+    <row r="226" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="C226" s="7">
+        <v>46325</v>
+      </c>
       <c r="D226" s="6"/>
       <c r="E226" s="6"/>
       <c r="F226" s="6"/>
@@ -40411,10 +42074,16 @@
       <c r="Y226" s="6"/>
       <c r="Z226" s="6"/>
     </row>
-    <row r="227" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A227" s="6"/>
-      <c r="B227" s="6"/>
-      <c r="C227" s="8"/>
+    <row r="227" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="11" t="s">
+        <v>634</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C227" s="7">
+        <v>46326</v>
+      </c>
       <c r="D227" s="6"/>
       <c r="E227" s="6"/>
       <c r="F227" s="6"/>
@@ -40439,10 +42108,16 @@
       <c r="Y227" s="6"/>
       <c r="Z227" s="6"/>
     </row>
-    <row r="228" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A228" s="6"/>
-      <c r="B228" s="6"/>
-      <c r="C228" s="8"/>
+    <row r="228" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C228" s="7">
+        <v>46327</v>
+      </c>
       <c r="D228" s="6"/>
       <c r="E228" s="6"/>
       <c r="F228" s="6"/>
@@ -40467,10 +42142,16 @@
       <c r="Y228" s="6"/>
       <c r="Z228" s="6"/>
     </row>
-    <row r="229" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A229" s="6"/>
-      <c r="B229" s="6"/>
-      <c r="C229" s="8"/>
+    <row r="229" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="C229" s="7">
+        <v>46328</v>
+      </c>
       <c r="D229" s="6"/>
       <c r="E229" s="6"/>
       <c r="F229" s="6"/>
@@ -40495,10 +42176,16 @@
       <c r="Y229" s="6"/>
       <c r="Z229" s="6"/>
     </row>
-    <row r="230" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A230" s="6"/>
-      <c r="B230" s="6"/>
-      <c r="C230" s="8"/>
+    <row r="230" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="C230" s="7">
+        <v>46329</v>
+      </c>
       <c r="D230" s="6"/>
       <c r="E230" s="6"/>
       <c r="F230" s="6"/>
@@ -40523,10 +42210,16 @@
       <c r="Y230" s="6"/>
       <c r="Z230" s="6"/>
     </row>
-    <row r="231" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A231" s="6"/>
-      <c r="B231" s="6"/>
-      <c r="C231" s="8"/>
+    <row r="231" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="C231" s="7">
+        <v>46330</v>
+      </c>
       <c r="D231" s="6"/>
       <c r="E231" s="6"/>
       <c r="F231" s="6"/>
@@ -40551,10 +42244,16 @@
       <c r="Y231" s="6"/>
       <c r="Z231" s="6"/>
     </row>
-    <row r="232" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A232" s="6"/>
-      <c r="B232" s="6"/>
-      <c r="C232" s="8"/>
+    <row r="232" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="C232" s="7">
+        <v>46331</v>
+      </c>
       <c r="D232" s="6"/>
       <c r="E232" s="6"/>
       <c r="F232" s="6"/>
@@ -40579,10 +42278,16 @@
       <c r="Y232" s="6"/>
       <c r="Z232" s="6"/>
     </row>
-    <row r="233" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A233" s="6"/>
-      <c r="B233" s="6"/>
-      <c r="C233" s="8"/>
+    <row r="233" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="C233" s="7">
+        <v>46332</v>
+      </c>
       <c r="D233" s="6"/>
       <c r="E233" s="6"/>
       <c r="F233" s="6"/>
@@ -40607,10 +42312,16 @@
       <c r="Y233" s="6"/>
       <c r="Z233" s="6"/>
     </row>
-    <row r="234" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A234" s="6"/>
-      <c r="B234" s="6"/>
-      <c r="C234" s="8"/>
+    <row r="234" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="C234" s="7">
+        <v>46333</v>
+      </c>
       <c r="D234" s="6"/>
       <c r="E234" s="6"/>
       <c r="F234" s="6"/>
@@ -40635,10 +42346,16 @@
       <c r="Y234" s="6"/>
       <c r="Z234" s="6"/>
     </row>
-    <row r="235" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A235" s="6"/>
-      <c r="B235" s="6"/>
-      <c r="C235" s="8"/>
+    <row r="235" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="11" t="s">
+        <v>642</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="C235" s="7">
+        <v>46334</v>
+      </c>
       <c r="D235" s="6"/>
       <c r="E235" s="6"/>
       <c r="F235" s="6"/>
@@ -40663,10 +42380,16 @@
       <c r="Y235" s="6"/>
       <c r="Z235" s="6"/>
     </row>
-    <row r="236" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A236" s="6"/>
-      <c r="B236" s="6"/>
-      <c r="C236" s="8"/>
+    <row r="236" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="C236" s="7">
+        <v>46335</v>
+      </c>
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
       <c r="F236" s="6"/>
@@ -40691,10 +42414,16 @@
       <c r="Y236" s="6"/>
       <c r="Z236" s="6"/>
     </row>
-    <row r="237" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A237" s="6"/>
-      <c r="B237" s="6"/>
-      <c r="C237" s="8"/>
+    <row r="237" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A237" s="11" t="s">
+        <v>643</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="C237" s="7">
+        <v>46336</v>
+      </c>
       <c r="D237" s="6"/>
       <c r="E237" s="6"/>
       <c r="F237" s="6"/>
@@ -40719,10 +42448,16 @@
       <c r="Y237" s="6"/>
       <c r="Z237" s="6"/>
     </row>
-    <row r="238" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A238" s="6"/>
-      <c r="B238" s="6"/>
-      <c r="C238" s="8"/>
+    <row r="238" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A238" s="11" t="s">
+        <v>644</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="C238" s="7">
+        <v>46337</v>
+      </c>
       <c r="D238" s="6"/>
       <c r="E238" s="6"/>
       <c r="F238" s="6"/>
@@ -40747,10 +42482,16 @@
       <c r="Y238" s="6"/>
       <c r="Z238" s="6"/>
     </row>
-    <row r="239" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A239" s="6"/>
-      <c r="B239" s="6"/>
-      <c r="C239" s="8"/>
+    <row r="239" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A239" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="C239" s="7">
+        <v>46338</v>
+      </c>
       <c r="D239" s="6"/>
       <c r="E239" s="6"/>
       <c r="F239" s="6"/>
@@ -40775,10 +42516,16 @@
       <c r="Y239" s="6"/>
       <c r="Z239" s="6"/>
     </row>
-    <row r="240" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A240" s="6"/>
-      <c r="B240" s="6"/>
-      <c r="C240" s="8"/>
+    <row r="240" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="11" t="s">
+        <v>646</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="C240" s="7">
+        <v>46339</v>
+      </c>
       <c r="D240" s="6"/>
       <c r="E240" s="6"/>
       <c r="F240" s="6"/>
@@ -40803,10 +42550,16 @@
       <c r="Y240" s="6"/>
       <c r="Z240" s="6"/>
     </row>
-    <row r="241" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A241" s="6"/>
-      <c r="B241" s="6"/>
-      <c r="C241" s="8"/>
+    <row r="241" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="11" t="s">
+        <v>647</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="C241" s="7">
+        <v>46340</v>
+      </c>
       <c r="D241" s="6"/>
       <c r="E241" s="6"/>
       <c r="F241" s="6"/>
@@ -40831,10 +42584,16 @@
       <c r="Y241" s="6"/>
       <c r="Z241" s="6"/>
     </row>
-    <row r="242" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A242" s="6"/>
-      <c r="B242" s="6"/>
-      <c r="C242" s="8"/>
+    <row r="242" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A242" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="C242" s="7">
+        <v>46341</v>
+      </c>
       <c r="D242" s="6"/>
       <c r="E242" s="6"/>
       <c r="F242" s="6"/>
@@ -40859,10 +42618,16 @@
       <c r="Y242" s="6"/>
       <c r="Z242" s="6"/>
     </row>
-    <row r="243" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A243" s="6"/>
-      <c r="B243" s="6"/>
-      <c r="C243" s="8"/>
+    <row r="243" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A243" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="C243" s="7">
+        <v>46342</v>
+      </c>
       <c r="D243" s="6"/>
       <c r="E243" s="6"/>
       <c r="F243" s="6"/>
@@ -40887,10 +42652,16 @@
       <c r="Y243" s="6"/>
       <c r="Z243" s="6"/>
     </row>
-    <row r="244" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A244" s="6"/>
-      <c r="B244" s="6"/>
-      <c r="C244" s="8"/>
+    <row r="244" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="11" t="s">
+        <v>649</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="C244" s="7">
+        <v>46343</v>
+      </c>
       <c r="D244" s="6"/>
       <c r="E244" s="6"/>
       <c r="F244" s="6"/>
@@ -40915,10 +42686,16 @@
       <c r="Y244" s="6"/>
       <c r="Z244" s="6"/>
     </row>
-    <row r="245" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A245" s="6"/>
-      <c r="B245" s="6"/>
-      <c r="C245" s="8"/>
+    <row r="245" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="11" t="s">
+        <v>650</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="C245" s="7">
+        <v>46344</v>
+      </c>
       <c r="D245" s="6"/>
       <c r="E245" s="6"/>
       <c r="F245" s="6"/>
@@ -40943,10 +42720,16 @@
       <c r="Y245" s="6"/>
       <c r="Z245" s="6"/>
     </row>
-    <row r="246" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A246" s="6"/>
-      <c r="B246" s="6"/>
-      <c r="C246" s="8"/>
+    <row r="246" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A246" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="C246" s="7">
+        <v>46345</v>
+      </c>
       <c r="D246" s="6"/>
       <c r="E246" s="6"/>
       <c r="F246" s="6"/>
@@ -40971,10 +42754,16 @@
       <c r="Y246" s="6"/>
       <c r="Z246" s="6"/>
     </row>
-    <row r="247" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A247" s="6"/>
-      <c r="B247" s="6"/>
-      <c r="C247" s="8"/>
+    <row r="247" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A247" s="11" t="s">
+        <v>652</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="C247" s="7">
+        <v>46346</v>
+      </c>
       <c r="D247" s="6"/>
       <c r="E247" s="6"/>
       <c r="F247" s="6"/>
@@ -40999,10 +42788,16 @@
       <c r="Y247" s="6"/>
       <c r="Z247" s="6"/>
     </row>
-    <row r="248" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A248" s="6"/>
-      <c r="B248" s="6"/>
-      <c r="C248" s="8"/>
+    <row r="248" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A248" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="C248" s="7">
+        <v>46347</v>
+      </c>
       <c r="D248" s="6"/>
       <c r="E248" s="6"/>
       <c r="F248" s="6"/>
@@ -41027,10 +42822,16 @@
       <c r="Y248" s="6"/>
       <c r="Z248" s="6"/>
     </row>
-    <row r="249" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A249" s="6"/>
-      <c r="B249" s="6"/>
-      <c r="C249" s="8"/>
+    <row r="249" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A249" s="11" t="s">
+        <v>654</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="C249" s="7">
+        <v>46348</v>
+      </c>
       <c r="D249" s="6"/>
       <c r="E249" s="6"/>
       <c r="F249" s="6"/>
@@ -41055,10 +42856,16 @@
       <c r="Y249" s="6"/>
       <c r="Z249" s="6"/>
     </row>
-    <row r="250" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A250" s="6"/>
-      <c r="B250" s="6"/>
-      <c r="C250" s="8"/>
+    <row r="250" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="11" t="s">
+        <v>655</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="C250" s="7">
+        <v>46349</v>
+      </c>
       <c r="D250" s="6"/>
       <c r="E250" s="6"/>
       <c r="F250" s="6"/>
@@ -41083,10 +42890,16 @@
       <c r="Y250" s="6"/>
       <c r="Z250" s="6"/>
     </row>
-    <row r="251" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A251" s="6"/>
-      <c r="B251" s="6"/>
-      <c r="C251" s="8"/>
+    <row r="251" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A251" s="11" t="s">
+        <v>656</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="C251" s="7">
+        <v>46350</v>
+      </c>
       <c r="D251" s="6"/>
       <c r="E251" s="6"/>
       <c r="F251" s="6"/>
@@ -41111,10 +42924,16 @@
       <c r="Y251" s="6"/>
       <c r="Z251" s="6"/>
     </row>
-    <row r="252" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A252" s="6"/>
-      <c r="B252" s="6"/>
-      <c r="C252" s="8"/>
+    <row r="252" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A252" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="C252" s="7">
+        <v>46351</v>
+      </c>
       <c r="D252" s="6"/>
       <c r="E252" s="6"/>
       <c r="F252" s="6"/>
@@ -41139,10 +42958,16 @@
       <c r="Y252" s="6"/>
       <c r="Z252" s="6"/>
     </row>
-    <row r="253" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A253" s="6"/>
-      <c r="B253" s="6"/>
-      <c r="C253" s="8"/>
+    <row r="253" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="11" t="s">
+        <v>658</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="C253" s="7">
+        <v>46352</v>
+      </c>
       <c r="D253" s="6"/>
       <c r="E253" s="6"/>
       <c r="F253" s="6"/>
@@ -41167,10 +42992,16 @@
       <c r="Y253" s="6"/>
       <c r="Z253" s="6"/>
     </row>
-    <row r="254" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="6"/>
-      <c r="B254" s="6"/>
-      <c r="C254" s="8"/>
+    <row r="254" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A254" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="C254" s="7">
+        <v>46353</v>
+      </c>
       <c r="D254" s="6"/>
       <c r="E254" s="6"/>
       <c r="F254" s="6"/>
@@ -41195,10 +43026,16 @@
       <c r="Y254" s="6"/>
       <c r="Z254" s="6"/>
     </row>
-    <row r="255" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A255" s="6"/>
-      <c r="B255" s="6"/>
-      <c r="C255" s="8"/>
+    <row r="255" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A255" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="C255" s="7">
+        <v>46354</v>
+      </c>
       <c r="D255" s="6"/>
       <c r="E255" s="6"/>
       <c r="F255" s="6"/>
@@ -41223,10 +43060,16 @@
       <c r="Y255" s="6"/>
       <c r="Z255" s="6"/>
     </row>
-    <row r="256" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A256" s="6"/>
-      <c r="B256" s="6"/>
-      <c r="C256" s="8"/>
+    <row r="256" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A256" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="C256" s="7">
+        <v>46355</v>
+      </c>
       <c r="D256" s="6"/>
       <c r="E256" s="6"/>
       <c r="F256" s="6"/>
@@ -41251,10 +43094,16 @@
       <c r="Y256" s="6"/>
       <c r="Z256" s="6"/>
     </row>
-    <row r="257" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A257" s="6"/>
-      <c r="B257" s="6"/>
-      <c r="C257" s="8"/>
+    <row r="257" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="11" t="s">
+        <v>662</v>
+      </c>
+      <c r="B257" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="C257" s="7">
+        <v>46356</v>
+      </c>
       <c r="D257" s="6"/>
       <c r="E257" s="6"/>
       <c r="F257" s="6"/>
@@ -41279,10 +43128,16 @@
       <c r="Y257" s="6"/>
       <c r="Z257" s="6"/>
     </row>
-    <row r="258" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A258" s="6"/>
-      <c r="B258" s="6"/>
-      <c r="C258" s="8"/>
+    <row r="258" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A258" s="11" t="s">
+        <v>663</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="C258" s="7">
+        <v>46357</v>
+      </c>
       <c r="D258" s="6"/>
       <c r="E258" s="6"/>
       <c r="F258" s="6"/>
@@ -41307,10 +43162,16 @@
       <c r="Y258" s="6"/>
       <c r="Z258" s="6"/>
     </row>
-    <row r="259" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A259" s="6"/>
-      <c r="B259" s="6"/>
-      <c r="C259" s="8"/>
+    <row r="259" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="11" t="s">
+        <v>664</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="C259" s="7">
+        <v>46358</v>
+      </c>
       <c r="D259" s="6"/>
       <c r="E259" s="6"/>
       <c r="F259" s="6"/>
@@ -41335,10 +43196,16 @@
       <c r="Y259" s="6"/>
       <c r="Z259" s="6"/>
     </row>
-    <row r="260" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A260" s="6"/>
-      <c r="B260" s="6"/>
-      <c r="C260" s="8"/>
+    <row r="260" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A260" s="11" t="s">
+        <v>665</v>
+      </c>
+      <c r="B260" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="C260" s="7">
+        <v>46359</v>
+      </c>
       <c r="D260" s="6"/>
       <c r="E260" s="6"/>
       <c r="F260" s="6"/>
@@ -41363,10 +43230,16 @@
       <c r="Y260" s="6"/>
       <c r="Z260" s="6"/>
     </row>
-    <row r="261" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A261" s="6"/>
-      <c r="B261" s="6"/>
-      <c r="C261" s="8"/>
+    <row r="261" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A261" s="11" t="s">
+        <v>666</v>
+      </c>
+      <c r="B261" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="C261" s="7">
+        <v>46360</v>
+      </c>
       <c r="D261" s="6"/>
       <c r="E261" s="6"/>
       <c r="F261" s="6"/>
@@ -41391,10 +43264,16 @@
       <c r="Y261" s="6"/>
       <c r="Z261" s="6"/>
     </row>
-    <row r="262" spans="1:26" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A262" s="6"/>
-      <c r="B262" s="6"/>
-      <c r="C262" s="8"/>
+    <row r="262" spans="1:26" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A262" s="11" t="s">
+        <v>667</v>
+      </c>
+      <c r="B262" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="C262" s="7">
+        <v>46361</v>
+      </c>
       <c r="D262" s="6"/>
       <c r="E262" s="6"/>
       <c r="F262" s="6"/>
@@ -60802,6 +62681,67 @@
     <hyperlink ref="A199" r:id="rId198" display="https://www.youtube.com/watch?v=7rdJOSgHgg4&amp;t=559s" xr:uid="{5AE9086F-C88B-4904-B4B1-017E953B6112}"/>
     <hyperlink ref="A200" r:id="rId199" xr:uid="{F88CFF51-F646-4EC3-B430-19E5215C4A65}"/>
     <hyperlink ref="A201" r:id="rId200" display="https://www.youtube.com/watch?v=tS58CDMrFxA&amp;t=23s" xr:uid="{9C56800F-7A09-4835-95ED-C639EFD179DF}"/>
+    <hyperlink ref="A202" r:id="rId201" xr:uid="{F0F1998F-0FAF-4C72-8D44-168B6FDB72ED}"/>
+    <hyperlink ref="A203" r:id="rId202" display="https://www.youtube.com/watch?v=iT7CUPzFbRQ&amp;t=9s" xr:uid="{0454C535-00B8-4DF7-ACB0-BBE91C33F553}"/>
+    <hyperlink ref="A204" r:id="rId203" display="https://www.youtube.com/watch?v=vuSYcVsLKhY&amp;t=1531s" xr:uid="{C8C04C5D-617E-4210-AAB0-8356051222D1}"/>
+    <hyperlink ref="A205" r:id="rId204" display="https://www.youtube.com/watch?v=MJsviZtSPFc&amp;t=12s" xr:uid="{B4BFA799-6066-49F2-B425-D67E2A87E2E6}"/>
+    <hyperlink ref="A206" r:id="rId205" display="https://www.youtube.com/watch?v=Ya86jfgQxPU&amp;t=49s" xr:uid="{C4940DBE-493C-4EDD-8DB7-96E95D777B2D}"/>
+    <hyperlink ref="A207" r:id="rId206" display="https://www.youtube.com/watch?v=jJSRiLY_hKo&amp;t=2s" xr:uid="{ED81996B-80FA-44FA-AB81-529A6F199B3F}"/>
+    <hyperlink ref="A208" r:id="rId207" display="https://www.youtube.com/watch?v=-NHHdVWUcwo&amp;t=2s" xr:uid="{0F59F9D3-E26D-4206-B46E-CD5C3E5B362C}"/>
+    <hyperlink ref="A209" r:id="rId208" display="https://www.youtube.com/watch?v=1fPXxQTCPKQ&amp;t=1s" xr:uid="{9DEC5847-7C23-45A6-B216-F3CD59F62920}"/>
+    <hyperlink ref="A210" r:id="rId209" xr:uid="{7CE0C133-D88B-455B-87A0-81F824594342}"/>
+    <hyperlink ref="A211" r:id="rId210" xr:uid="{00587B64-3BAC-4BC2-BE76-112121F51583}"/>
+    <hyperlink ref="A212" r:id="rId211" xr:uid="{D012AF6E-C14E-4791-9EF5-7FA4A493A48C}"/>
+    <hyperlink ref="A213" r:id="rId212" xr:uid="{1933B687-EEAB-4F66-8FC1-182414B0E935}"/>
+    <hyperlink ref="A214" r:id="rId213" display="https://www.youtube.com/watch?v=G3QwYAUfSQY&amp;t=3s" xr:uid="{B4383AF3-C14E-41F8-BBC8-07642BAAF544}"/>
+    <hyperlink ref="A215" r:id="rId214" display="https://www.youtube.com/watch?v=3OuM3M9TXkg&amp;t=1s" xr:uid="{16CF10C0-E7B4-4A0D-A292-4CFB1D5D62DE}"/>
+    <hyperlink ref="A216" r:id="rId215" xr:uid="{07699CDA-F537-4460-86CA-5154986EF6B8}"/>
+    <hyperlink ref="A217" r:id="rId216" display="https://www.youtube.com/watch?v=XDoquCuFKGk&amp;t=242s" xr:uid="{B3FCEAA2-510B-4FA6-81DA-B70E14DDCA46}"/>
+    <hyperlink ref="A218" r:id="rId217" display="https://www.youtube.com/watch?v=qYqJ9IOnwBY&amp;t=47s" xr:uid="{885E309A-0F8A-48F5-A40D-3EBE1037C509}"/>
+    <hyperlink ref="A219" r:id="rId218" xr:uid="{3A782E4E-1FE3-49E4-8137-5A65177F3847}"/>
+    <hyperlink ref="A220" r:id="rId219" display="https://www.youtube.com/watch?v=Ne58ALWRs68&amp;t=46s" xr:uid="{A7BD1AD2-A397-4AFB-BA0A-15444E562D11}"/>
+    <hyperlink ref="A221" r:id="rId220" display="https://www.youtube.com/watch?v=hE9f3FTjhog&amp;t=28s" xr:uid="{91F55023-E994-4301-A621-2473B1491DFC}"/>
+    <hyperlink ref="A222" r:id="rId221" xr:uid="{D30DDA5D-4445-4793-B5BA-73C37DD3BC23}"/>
+    <hyperlink ref="A223" r:id="rId222" display="https://www.youtube.com/watch?v=8siMw00cRt8&amp;t=1s" xr:uid="{3CB87BA0-D204-4AD9-B7AD-5FF460E95D7A}"/>
+    <hyperlink ref="A224" r:id="rId223" display="https://www.youtube.com/watch?v=Q24FZ2FRwGQ&amp;t=2s" xr:uid="{EAA2C594-4149-4A04-8C4F-C96F75B39B5C}"/>
+    <hyperlink ref="A225" r:id="rId224" xr:uid="{42248763-7ABF-4119-9B9C-30E2318B9C36}"/>
+    <hyperlink ref="A226" r:id="rId225" display="https://www.youtube.com/watch?v=GTeBLRi-Hho&amp;t=1s" xr:uid="{B3884C0D-A2B2-4F48-AAF3-A73374265B8F}"/>
+    <hyperlink ref="A227" r:id="rId226" display="https://www.youtube.com/watch?v=AW19y7ztyKs&amp;t=1361s" xr:uid="{2849E743-6226-4033-87DB-5B30B0E90304}"/>
+    <hyperlink ref="A228" r:id="rId227" display="https://www.youtube.com/watch?v=nbGi3a_tyi0&amp;t=2s" xr:uid="{E92BDAE8-A797-41AE-BF6B-4A49EDC55923}"/>
+    <hyperlink ref="A229" r:id="rId228" display="https://www.youtube.com/watch?v=QqTdOn-fxO4&amp;t=18s" xr:uid="{DF865311-BC38-40D8-997E-DBAC52D59BFD}"/>
+    <hyperlink ref="A230" r:id="rId229" display="https://www.youtube.com/watch?v=z2dGDx3u5p0&amp;t=232s" xr:uid="{F30DE7EC-DD34-451E-94B9-393176B2AEC1}"/>
+    <hyperlink ref="A231" r:id="rId230" display="https://www.youtube.com/watch?v=rPfM-T7cae8&amp;t=1s" xr:uid="{D508E26E-3F83-4D34-BE53-40E0DAA7AED2}"/>
+    <hyperlink ref="A232" r:id="rId231" xr:uid="{CBD26979-496D-4B30-9AB1-60505F9E6DD4}"/>
+    <hyperlink ref="A233" r:id="rId232" display="https://www.youtube.com/watch?v=HLgoQEBcm6o&amp;t=125s" xr:uid="{E8F63D81-9A4F-4233-B18A-9EE3CF73B43B}"/>
+    <hyperlink ref="A234" r:id="rId233" display="https://www.youtube.com/watch?v=ruWNJ2f_KJs&amp;t=16s" xr:uid="{E5A38B11-49D6-4A50-A036-46560C9EDF77}"/>
+    <hyperlink ref="A235" r:id="rId234" xr:uid="{A422D850-EA14-439D-A7B6-CAEE423082A0}"/>
+    <hyperlink ref="A236" r:id="rId235" display="https://www.youtube.com/watch?v=ixeML2iYD3w&amp;t=3s" xr:uid="{7E5F0D5B-CABF-4ADB-A004-45D848A2CB45}"/>
+    <hyperlink ref="A237" r:id="rId236" xr:uid="{F35B05E8-BB0E-4924-8604-EF978AFB8F3B}"/>
+    <hyperlink ref="A238" r:id="rId237" display="https://www.youtube.com/watch?v=Lxwh9fSrLfo&amp;t=4s" xr:uid="{736EDA74-5866-4CDD-8F29-06669FD95EAB}"/>
+    <hyperlink ref="A239" r:id="rId238" xr:uid="{DAAA6546-84C9-476C-B45E-79360B3E5F76}"/>
+    <hyperlink ref="A240" r:id="rId239" display="https://www.youtube.com/watch?v=Yjc7P_-Yuhg&amp;t=42s" xr:uid="{15A86D18-C236-463A-B8E3-F7C15352B793}"/>
+    <hyperlink ref="A241" r:id="rId240" display="https://www.youtube.com/watch?v=Mv14PuzubPs&amp;t=2s" xr:uid="{BDD99A1E-8E99-4D66-8372-0EFA63F1FEC0}"/>
+    <hyperlink ref="A242" r:id="rId241" display="https://www.youtube.com/watch?v=vVvHXSohHwA&amp;t=4s" xr:uid="{ED1A0BBE-F380-4AFF-B6DF-E0E604E79F17}"/>
+    <hyperlink ref="A243" r:id="rId242" display="https://www.youtube.com/watch?v=vVvHXSohHwA&amp;t=4s" xr:uid="{EC1861EF-36D3-42EA-8710-5D524C78BF76}"/>
+    <hyperlink ref="A244" r:id="rId243" xr:uid="{41D3B8BB-DD98-4DAE-90AD-6EE827FE76B6}"/>
+    <hyperlink ref="A245" r:id="rId244" display="https://www.youtube.com/watch?v=TLaRnmjmabE&amp;t=2s" xr:uid="{7017369D-9B86-4F4C-B7CC-6B7DC13AB265}"/>
+    <hyperlink ref="A246" r:id="rId245" display="https://www.youtube.com/watch?v=8LGfGpiD-Mk&amp;t=11s" xr:uid="{EF3BACC6-79A9-4D3F-B1FA-E2D78682A63E}"/>
+    <hyperlink ref="A247" r:id="rId246" display="https://www.youtube.com/watch?v=NrBla1RTvTE&amp;t=29s" xr:uid="{4227E2E6-CE42-4677-93B7-2978C4F16496}"/>
+    <hyperlink ref="A248" r:id="rId247" xr:uid="{0810E6BD-D0BA-4942-9DA1-18CA653A198E}"/>
+    <hyperlink ref="A249" r:id="rId248" xr:uid="{C824F04C-8CD1-400C-AD08-10579800EFC3}"/>
+    <hyperlink ref="A250" r:id="rId249" xr:uid="{FD2D76B4-4B98-43BA-943E-276CC21CAEEC}"/>
+    <hyperlink ref="A251" r:id="rId250" xr:uid="{0E0A4460-1F7A-4B85-B7FD-2C2692002E75}"/>
+    <hyperlink ref="A252" r:id="rId251" display="https://www.youtube.com/watch?v=Ai0jdNcEMHw&amp;t=5s" xr:uid="{3C0819E2-C214-40BC-9B90-023F17B85238}"/>
+    <hyperlink ref="A253" r:id="rId252" xr:uid="{702C96A7-442B-43E1-B307-28C54E76B191}"/>
+    <hyperlink ref="A254" r:id="rId253" xr:uid="{2F349440-3EC9-4718-8A8C-149B8A451C94}"/>
+    <hyperlink ref="A255" r:id="rId254" xr:uid="{728FA886-D822-4BF8-9418-40D011DF17C2}"/>
+    <hyperlink ref="A256" r:id="rId255" xr:uid="{6CF9FD08-B849-4AD9-BE5A-351D7BB2E5E0}"/>
+    <hyperlink ref="A257" r:id="rId256" xr:uid="{D910A5AB-C00B-421D-841B-7B7962222E51}"/>
+    <hyperlink ref="A258" r:id="rId257" xr:uid="{4E1EB864-F84B-40A8-9BB7-F5D21C2AE85C}"/>
+    <hyperlink ref="A259" r:id="rId258" xr:uid="{3412EC0F-5DF0-4E52-95C9-EA963A8CE666}"/>
+    <hyperlink ref="A260" r:id="rId259" xr:uid="{94CFA422-DF77-4983-8684-8A4CE332C852}"/>
+    <hyperlink ref="A261" r:id="rId260" xr:uid="{B671E917-6C37-47A2-988B-239C70D16E7C}"/>
+    <hyperlink ref="A262" r:id="rId261" xr:uid="{CBAC30E2-F786-473E-83E8-178F31E67EFB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/Daily Sadhana.xlsx
+++ b/public/Daily Sadhana.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sahaa\Documents\github_anandasvarupa\give_web\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{567053E3-F29A-4970-A043-06ADD0DB464C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1752A59-98D1-47C7-831C-9FBDB67F4426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BS-4" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="768">
   <si>
     <t>url</t>
   </si>
@@ -2215,6 +2215,123 @@
   </si>
   <si>
     <t>Today's listening to Srila Prabhupada - 350</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1163</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1164</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1165</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1166</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1167</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1168</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1169</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1170</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1171</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1172</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1173</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1174</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1175</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1176</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1177</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1178</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1179</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1180</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1181</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1182</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1183</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1184</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1185</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1186</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1187</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1188</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1189</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1190</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1191</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1192</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1193</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1194</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1195</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1196</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1197</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1198</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1199</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1200</t>
+  </si>
+  <si>
+    <t>Today's listening to Srila Prabhupada - 1201</t>
   </si>
 </sst>
 </file>
@@ -62749,7 +62866,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2DB8064-9FCF-4672-A5DD-AAA1AF5AE7B8}">
-  <dimension ref="A1:Z44"/>
+  <dimension ref="A1:Z83"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.90625" customWidth="1"/>
@@ -63254,7 +63371,7 @@
         <v>46321</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>583</v>
       </c>
@@ -63263,6 +63380,435 @@
       </c>
       <c r="C44" s="7">
         <v>46322</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>729</v>
+      </c>
+      <c r="C45" s="7">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
+        <v>632</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="C46" s="7">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="C47" s="7">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="11" t="s">
+        <v>634</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="C48" s="7">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="C49" s="7">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>734</v>
+      </c>
+      <c r="C50" s="7">
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>735</v>
+      </c>
+      <c r="C51" s="7">
+        <v>46329</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="C52" s="7">
+        <v>46330</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>737</v>
+      </c>
+      <c r="C53" s="7">
+        <v>46331</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>738</v>
+      </c>
+      <c r="C54" s="7">
+        <v>46332</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="C55" s="7">
+        <v>46333</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="11" t="s">
+        <v>642</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="C56" s="7">
+        <v>46334</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="C57" s="7">
+        <v>46335</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="11" t="s">
+        <v>643</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="C58" s="7">
+        <v>46336</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="11" t="s">
+        <v>644</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="C59" s="7">
+        <v>46337</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="C60" s="7">
+        <v>46338</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="11" t="s">
+        <v>646</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="C61" s="7">
+        <v>46339</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="11" t="s">
+        <v>647</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="C62" s="7">
+        <v>46340</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>747</v>
+      </c>
+      <c r="C63" s="7">
+        <v>46341</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="C64" s="7">
+        <v>46342</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="11" t="s">
+        <v>649</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="C65" s="7">
+        <v>46343</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="11" t="s">
+        <v>650</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="C66" s="7">
+        <v>46344</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="C67" s="7">
+        <v>46345</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="11" t="s">
+        <v>652</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="C68" s="7">
+        <v>46346</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>753</v>
+      </c>
+      <c r="C69" s="7">
+        <v>46347</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="11" t="s">
+        <v>654</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="C70" s="7">
+        <v>46348</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="11" t="s">
+        <v>655</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>755</v>
+      </c>
+      <c r="C71" s="7">
+        <v>46349</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="11" t="s">
+        <v>656</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="C72" s="7">
+        <v>46350</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="C73" s="7">
+        <v>46351</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="11" t="s">
+        <v>658</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="C74" s="7">
+        <v>46352</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="C75" s="7">
+        <v>46353</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="C76" s="7">
+        <v>46354</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="C77" s="7">
+        <v>46355</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="11" t="s">
+        <v>662</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="C78" s="7">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="11" t="s">
+        <v>663</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="C79" s="7">
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="11" t="s">
+        <v>664</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="C80" s="7">
+        <v>46358</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="11" t="s">
+        <v>665</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="C81" s="7">
+        <v>46359</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="11" t="s">
+        <v>666</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="C82" s="7">
+        <v>46360</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="11" t="s">
+        <v>667</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>767</v>
+      </c>
+      <c r="C83" s="7">
+        <v>46361</v>
       </c>
     </row>
   </sheetData>
@@ -63270,6 +63816,45 @@
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.youtube.com/watch?v=1Ilgi75Y6Ac&amp;t=9s" xr:uid="{BEFFE2FC-FF84-4042-B8EC-77144312CABC}"/>
     <hyperlink ref="A18" r:id="rId2" xr:uid="{266B1484-6826-4EF7-BFC0-E28E4199D83A}"/>
+    <hyperlink ref="A45" r:id="rId3" display="https://www.youtube.com/watch?v=Q24FZ2FRwGQ&amp;t=2s" xr:uid="{132FBFEE-56E3-4393-A4C6-D75016DECC29}"/>
+    <hyperlink ref="A46" r:id="rId4" xr:uid="{F50F6529-F0E8-4C70-A13D-64367A3A8066}"/>
+    <hyperlink ref="A47" r:id="rId5" display="https://www.youtube.com/watch?v=GTeBLRi-Hho&amp;t=1s" xr:uid="{08280529-3F60-4E29-9683-56CCE4D785D9}"/>
+    <hyperlink ref="A48" r:id="rId6" display="https://www.youtube.com/watch?v=AW19y7ztyKs&amp;t=1361s" xr:uid="{2F24D67A-527A-42EB-8910-2D49F1E87267}"/>
+    <hyperlink ref="A49" r:id="rId7" display="https://www.youtube.com/watch?v=nbGi3a_tyi0&amp;t=2s" xr:uid="{BA98A2AA-F4DC-4721-825C-4EFFB99F8B60}"/>
+    <hyperlink ref="A50" r:id="rId8" display="https://www.youtube.com/watch?v=QqTdOn-fxO4&amp;t=18s" xr:uid="{6EC6C4FD-8A9E-4F63-9D8C-F3335BE857A1}"/>
+    <hyperlink ref="A51" r:id="rId9" display="https://www.youtube.com/watch?v=z2dGDx3u5p0&amp;t=232s" xr:uid="{094927C5-447D-484A-BF4E-69DA11389CD0}"/>
+    <hyperlink ref="A52" r:id="rId10" display="https://www.youtube.com/watch?v=rPfM-T7cae8&amp;t=1s" xr:uid="{AEFCAA98-2FCE-4780-AA44-19FDEEFDE769}"/>
+    <hyperlink ref="A53" r:id="rId11" xr:uid="{5AE56921-6AAA-4AFA-B693-CDBFB6B4D107}"/>
+    <hyperlink ref="A54" r:id="rId12" display="https://www.youtube.com/watch?v=HLgoQEBcm6o&amp;t=125s" xr:uid="{37B80CBE-A48B-4672-B873-4A5D3383646C}"/>
+    <hyperlink ref="A55" r:id="rId13" display="https://www.youtube.com/watch?v=ruWNJ2f_KJs&amp;t=16s" xr:uid="{9942A07B-20B4-4CF9-A895-E7385BC32252}"/>
+    <hyperlink ref="A56" r:id="rId14" xr:uid="{AD7C63DF-8694-442F-A572-0E9A33676ADF}"/>
+    <hyperlink ref="A57" r:id="rId15" display="https://www.youtube.com/watch?v=ixeML2iYD3w&amp;t=3s" xr:uid="{BE8D5C45-9812-49AB-BBE6-0ADC09C426C7}"/>
+    <hyperlink ref="A58" r:id="rId16" xr:uid="{4BECC1C1-FB72-4D41-87FA-3EF76F012D22}"/>
+    <hyperlink ref="A59" r:id="rId17" display="https://www.youtube.com/watch?v=Lxwh9fSrLfo&amp;t=4s" xr:uid="{328B722C-0890-4DDE-8923-7A4B693829A6}"/>
+    <hyperlink ref="A60" r:id="rId18" xr:uid="{F6A13145-8D1C-46AA-9704-75C787042891}"/>
+    <hyperlink ref="A61" r:id="rId19" display="https://www.youtube.com/watch?v=Yjc7P_-Yuhg&amp;t=42s" xr:uid="{8CDE1602-3610-48CC-A2D0-8FCB57A22C4E}"/>
+    <hyperlink ref="A62" r:id="rId20" display="https://www.youtube.com/watch?v=Mv14PuzubPs&amp;t=2s" xr:uid="{F7F537A8-25FC-40AF-A10F-7D99E2120F20}"/>
+    <hyperlink ref="A63" r:id="rId21" display="https://www.youtube.com/watch?v=vVvHXSohHwA&amp;t=4s" xr:uid="{6D51514D-3752-4AF6-8619-09747580DFBD}"/>
+    <hyperlink ref="A64" r:id="rId22" display="https://www.youtube.com/watch?v=vVvHXSohHwA&amp;t=4s" xr:uid="{72878EB1-2699-450D-80A7-0F9C56FD1062}"/>
+    <hyperlink ref="A65" r:id="rId23" xr:uid="{3DD03F44-C4FC-4920-9CD4-EDFA9F623382}"/>
+    <hyperlink ref="A66" r:id="rId24" display="https://www.youtube.com/watch?v=TLaRnmjmabE&amp;t=2s" xr:uid="{82A29091-339B-49F2-AFB8-B501A153A69D}"/>
+    <hyperlink ref="A67" r:id="rId25" display="https://www.youtube.com/watch?v=8LGfGpiD-Mk&amp;t=11s" xr:uid="{2E223C6A-DDD3-49AC-8FF7-27C3CC856A44}"/>
+    <hyperlink ref="A68" r:id="rId26" display="https://www.youtube.com/watch?v=NrBla1RTvTE&amp;t=29s" xr:uid="{2B543A47-D491-44D9-ABCE-633213094941}"/>
+    <hyperlink ref="A69" r:id="rId27" xr:uid="{89AD0F73-85FA-483A-A254-5737A41B9834}"/>
+    <hyperlink ref="A70" r:id="rId28" xr:uid="{CD96F33B-8959-4F6A-B4D0-CFE7EA0265D3}"/>
+    <hyperlink ref="A71" r:id="rId29" xr:uid="{9C13BEFC-47F7-4727-9E09-034B59803FF2}"/>
+    <hyperlink ref="A72" r:id="rId30" xr:uid="{73ABE910-D2EF-4033-BE0E-73E900B50D1C}"/>
+    <hyperlink ref="A73" r:id="rId31" display="https://www.youtube.com/watch?v=Ai0jdNcEMHw&amp;t=5s" xr:uid="{F61408A1-CF32-473A-986E-2EF71CFAD396}"/>
+    <hyperlink ref="A74" r:id="rId32" xr:uid="{1577ACF6-79F3-4FE5-AEC5-983819FC0874}"/>
+    <hyperlink ref="A75" r:id="rId33" xr:uid="{2DA5147E-788D-4874-8CA4-AC1B4B921E94}"/>
+    <hyperlink ref="A76" r:id="rId34" xr:uid="{4FA474A0-92B8-4B33-A55E-90A47293767B}"/>
+    <hyperlink ref="A77" r:id="rId35" xr:uid="{6210D426-BED9-428D-9F42-25BB4934730B}"/>
+    <hyperlink ref="A78" r:id="rId36" xr:uid="{251C0452-33EC-42A1-BB0E-A4B0C5C69342}"/>
+    <hyperlink ref="A79" r:id="rId37" xr:uid="{9733D073-4C64-4755-9FF6-B7A256F84059}"/>
+    <hyperlink ref="A80" r:id="rId38" xr:uid="{631AB2C7-7C71-4BDB-84CE-4A4C255F65D4}"/>
+    <hyperlink ref="A81" r:id="rId39" xr:uid="{E0B9D2B7-76E4-40A7-975E-3B5174084D37}"/>
+    <hyperlink ref="A82" r:id="rId40" xr:uid="{61DE7A49-0711-4D44-8D25-E10CE16D756B}"/>
+    <hyperlink ref="A83" r:id="rId41" xr:uid="{7578719D-B46E-483D-8A0B-E16E12DBA4EC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
